--- a/data/raw/Kawak/2025.xlsx
+++ b/data/raw/Kawak/2025.xlsx
@@ -5,26 +5,38 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Indicadores_Oportunidad_Mejora/data/raw/Kawak/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://poligran-my.sharepoint.com/personal/lxisilva_poligran_edu_co/Documents/Documentos/Proyectos/Indicadores_Oportunidad_Mejora/data/raw/Kawak/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="8_{2553D8ED-1A7D-4653-A81C-B563898AD95F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9034F534-9D69-49FA-A187-A73F1C9A7441}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="8_{2553D8ED-1A7D-4653-A81C-B563898AD95F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CF02E1CE-4794-47A2-8D63-C2937FF371E0}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{0ABA65E9-32CA-4FC8-8179-9B0EBD2C31C1}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0ABA65E9-32CA-4FC8-8179-9B0EBD2C31C1}"/>
   </bookViews>
   <sheets>
     <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
-    <sheet name="Hoja1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Worksheet!$A$1:$Y$787</definedName>
   </definedNames>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12430" uniqueCount="1171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12429" uniqueCount="1171">
   <si>
     <t>Id</t>
   </si>
@@ -12560,7 +12572,9 @@
       <c r="M129" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="N129" s="3"/>
+      <c r="N129" s="3">
+        <v>197.94</v>
+      </c>
       <c r="O129" s="3"/>
       <c r="P129" s="3"/>
       <c r="Q129" s="3"/>
@@ -61151,1509 +61165,4 @@
   <pageSetup orientation="portrait"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3954112-B764-41D3-B005-6FD07A474463}">
-  <dimension ref="A1:A299"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" s="1">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" s="1">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" s="1">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" s="1">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" s="1">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A7" s="1">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A8" s="1">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A9" s="1">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A10" s="1">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A11" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A12" s="1">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A13" s="1">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A14" s="1">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A15" s="1">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A16" s="1">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" s="1">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18" s="1">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A19" s="1">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A20" s="1">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A21" s="1">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A22" s="1">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A23" s="1">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A24" s="1">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A25" s="1">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A26" s="1">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A27" s="1">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A28" s="1">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A29" s="1">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A30" s="1">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A31" s="1">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A32" s="1">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A33" s="1">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A34" s="1">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A35" s="1">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A36" s="1">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A37" s="1">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A38" s="1">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A39" s="1">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A40" s="1">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A41" s="1">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A42" s="1">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A43" s="1">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A44" s="1">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A45" s="1">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A46" s="1">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A47" s="1">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A48" s="1">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A49" s="1">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A50" s="1">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A51" s="1">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A52" s="1">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A53" s="1">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A54" s="1">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A55" s="1">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A56" s="1">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A57" s="1">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A58" s="1">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A59" s="1">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A60" s="1">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A61" s="1">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A62" s="1">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A63" s="1">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A64" s="1">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A65" s="1">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A66" s="1">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A67" s="1">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A68" s="1">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A69" s="1">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A70" s="1">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A71" s="1">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A72" s="1">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A73" s="1">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A74" s="1">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A75" s="1">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A76" s="1">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A77" s="1">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A78" s="1">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A79" s="1">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A80" s="1">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A81" s="1">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A82" s="1">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A83" s="1">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A84" s="1">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A85" s="1">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A86" s="1">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A87" s="1">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A88" s="1">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A89" s="1">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A90" s="1">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A91" s="1">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A92" s="1">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A93" s="1">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A94" s="1">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A95" s="1">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A96" s="1">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A97" s="1">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A98" s="1">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A99" s="1">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A100" s="1">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A101" s="1">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A102" s="1">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A103" s="1">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A104" s="1">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A105" s="1">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A106" s="1">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A107" s="1">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A108" s="1">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A109" s="1">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A110" s="1">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A111" s="1">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A112" s="1">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A113" s="1">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A114" s="1">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A115" s="1">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A116" s="1">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A117" s="1">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A118" s="1">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A119" s="1">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A120" s="1">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A121" s="1">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A122" s="1">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A123" s="1">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A124" s="1">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A125" s="1">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A126" s="1">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A127" s="1">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A128" s="1">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A129" s="1">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A130" s="1">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A131" s="1">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A132" s="1">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A133" s="1">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A134" s="1">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A135" s="1">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A136" s="1">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A137" s="1">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A138" s="1">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A139" s="1">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A140" s="1">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A141" s="1">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A142" s="1">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A143" s="1">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A144" s="1">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A145" s="1">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A146" s="1">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A147" s="1">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A148" s="1">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A149" s="1">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A150" s="1">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A151" s="1">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A152" s="1">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A153" s="1">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A154" s="1">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A155" s="1">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A156" s="1">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A157" s="1">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A158" s="1">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A159" s="1">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A160" s="1">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A161" s="1">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A162" s="1">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A163" s="1">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A164" s="1">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A165" s="1">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A166" s="1">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A167" s="1">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="168" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A168" s="1">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A169" s="1">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="170" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A170" s="1">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A171" s="1">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A172" s="1">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A173" s="1">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="174" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A174" s="1">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="175" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A175" s="1">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="176" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A176" s="1">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A177" s="1">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A178" s="1">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="179" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A179" s="1">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="180" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A180" s="1">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="181" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A181" s="1">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="182" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A182" s="1">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="183" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A183" s="1">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="184" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A184" s="1">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="185" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A185" s="1">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="186" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A186" s="1">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="187" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A187" s="1">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="188" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A188" s="1">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="189" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A189" s="1">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="190" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A190" s="1">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="191" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A191" s="1">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="192" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A192" s="1">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="193" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A193" s="1">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="194" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A194" s="1">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="195" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A195" s="1">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="196" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A196" s="1">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="197" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A197" s="1">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="198" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A198" s="1">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="199" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A199" s="1">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="200" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A200" s="1">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="201" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A201" s="1">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="202" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A202" s="1">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="203" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A203" s="1">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="204" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A204" s="1">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="205" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A205" s="1">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="206" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A206" s="1">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="207" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A207" s="1">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="208" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A208" s="1">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="209" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A209" s="1">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="210" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A210" s="1">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="211" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A211" s="1">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="212" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A212" s="1">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="213" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A213" s="1">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="214" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A214" s="1">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="215" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A215" s="1">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="216" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A216" s="1">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="217" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A217" s="1">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="218" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A218" s="1">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="219" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A219" s="1">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="220" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A220" s="1">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="221" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A221" s="1">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="222" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A222" s="1">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="223" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A223" s="1">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="224" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A224" s="1">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="225" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A225" s="1">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="226" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A226" s="1">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="227" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A227" s="1">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="228" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A228" s="1">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="229" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A229" s="1">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="230" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A230" s="1">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="231" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A231" s="1">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="232" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A232" s="1">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="233" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A233" s="1">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="234" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A234" s="1">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="235" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A235" s="1">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="236" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A236" s="1">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="237" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A237" s="1">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="238" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A238" s="1">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="239" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A239" s="1">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="240" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A240" s="1">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="241" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A241" s="1">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="242" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A242" s="1">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="243" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A243" s="1">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="244" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A244" s="1">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="245" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A245" s="1">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="246" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A246" s="1">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="247" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A247" s="1">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="248" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A248" s="1">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="249" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A249" s="1">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="250" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A250" s="1">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="251" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A251" s="1">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="252" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A252" s="1">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="253" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A253" s="1">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="254" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A254" s="1">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="255" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A255" s="1">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="256" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A256" s="1">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="257" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A257" s="1">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="258" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A258" s="1">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="259" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A259" s="1">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="260" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A260" s="1">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="261" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A261" s="1">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="262" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A262" s="1">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="263" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A263" s="1">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="264" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A264" s="1">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="265" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A265" s="1">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="266" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A266" s="1">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="267" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A267" s="1">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="268" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A268" s="1">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="269" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A269" s="1">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="270" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A270" s="1">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="271" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A271" s="1">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="272" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A272" s="1">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="273" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A273" s="1">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="274" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A274" s="1">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="275" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A275" s="1">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="276" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A276" s="1">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="277" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A277" s="1">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="278" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A278" s="1">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="279" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A279" s="1">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="280" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A280" s="1">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="281" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A281" s="1">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="282" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A282" s="1">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="283" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A283" s="1">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="284" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A284" s="1">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="285" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A285" s="1">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="286" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A286" s="1">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="287" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A287" s="1">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="288" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A288" s="1">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="289" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A289" s="1">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="290" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A290" s="1">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="291" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A291" s="1">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="292" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A292" s="1">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="293" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A293" s="1">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="294" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A294" s="1">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="295" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A295" s="1">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="296" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A296" s="1">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="297" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A297" s="1">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="298" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A298" s="1">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="299" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A299" s="1">
-        <v>529</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/data/raw/Kawak/2025.xlsx
+++ b/data/raw/Kawak/2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Indicadores_Oportunidad_Mejora/data/raw/Kawak/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="25" documentId="8_{2553D8ED-1A7D-4653-A81C-B563898AD95F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{06063DB0-60B4-47B0-A716-2AB6332D2EA1}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="8_{2553D8ED-1A7D-4653-A81C-B563898AD95F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8C83F3A3-C1B6-47B0-BEF7-0A4D43F5F290}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0ABA65E9-32CA-4FC8-8179-9B0EBD2C31C1}"/>
   </bookViews>
@@ -61102,6 +61102,7 @@
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
+  <autoFilter ref="A1:Y786" xr:uid="{69DEF77A-E506-4471-8935-B3BC88D629C9}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
   <headerFooter alignWithMargins="0"/>

--- a/data/raw/Kawak/2025.xlsx
+++ b/data/raw/Kawak/2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Indicadores_Oportunidad_Mejora/data/raw/Kawak/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:80000009_{8AFFF1CD-D2DA-4C63-96DB-380D859993A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:80000009_{8AFFF1CD-D2DA-4C63-96DB-380D859993A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A1B3DCF1-F8B0-49C4-8F13-6F3C3DC8C597}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8CDDBE38-F3DF-429A-BEB0-7E84F5F1A35B}"/>
   </bookViews>
@@ -3566,6 +3566,7 @@
       <sz val="11"/>
       <color indexed="8"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="9">
@@ -3648,7 +3649,16 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -4046,6 +4056,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B479DA7-9079-4551-A26B-76000E86CFA4}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:AA786"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4136,7 +4147,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>84</v>
       </c>
@@ -4206,7 +4217,7 @@
       <c r="W2" s="3"/>
       <c r="X2" s="3"/>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>85</v>
       </c>
@@ -4276,7 +4287,7 @@
       <c r="W3" s="3"/>
       <c r="X3" s="3"/>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>87</v>
       </c>
@@ -4346,7 +4357,7 @@
       <c r="W4" s="3"/>
       <c r="X4" s="3"/>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>88</v>
       </c>
@@ -4416,7 +4427,7 @@
       <c r="W5" s="3"/>
       <c r="X5" s="3"/>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>89</v>
       </c>
@@ -4486,7 +4497,7 @@
       <c r="W6" s="3"/>
       <c r="X6" s="3"/>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>90</v>
       </c>
@@ -4556,7 +4567,7 @@
       <c r="W7" s="3"/>
       <c r="X7" s="3"/>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>91</v>
       </c>
@@ -4626,7 +4637,7 @@
       <c r="W8" s="3"/>
       <c r="X8" s="3"/>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>92</v>
       </c>
@@ -4696,7 +4707,7 @@
       <c r="W9" s="3"/>
       <c r="X9" s="3"/>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>94</v>
       </c>
@@ -4766,7 +4777,7 @@
       <c r="W10" s="3"/>
       <c r="X10" s="3"/>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>100</v>
       </c>
@@ -4836,7 +4847,7 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>104</v>
       </c>
@@ -4906,7 +4917,7 @@
       <c r="W12" s="3"/>
       <c r="X12" s="3"/>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>106</v>
       </c>
@@ -4976,7 +4987,7 @@
       <c r="W13" s="3"/>
       <c r="X13" s="3"/>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>109</v>
       </c>
@@ -5045,7 +5056,7 @@
       <c r="Z14" s="3"/>
       <c r="AA14" s="3"/>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>112</v>
       </c>
@@ -5116,7 +5127,7 @@
       <c r="Z15" s="3"/>
       <c r="AA15" s="3"/>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>113</v>
       </c>
@@ -5258,7 +5269,7 @@
       <c r="Z17" s="3"/>
       <c r="AA17" s="3"/>
     </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>115</v>
       </c>
@@ -5329,7 +5340,7 @@
       <c r="Z18" s="3"/>
       <c r="AA18" s="3"/>
     </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>116</v>
       </c>
@@ -5392,7 +5403,7 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
     </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>117</v>
       </c>
@@ -5463,7 +5474,7 @@
       <c r="Z20" s="3"/>
       <c r="AA20" s="3"/>
     </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>118</v>
       </c>
@@ -5534,7 +5545,7 @@
       <c r="Z21" s="3"/>
       <c r="AA21" s="3"/>
     </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>126</v>
       </c>
@@ -5604,7 +5615,7 @@
       <c r="W22" s="3"/>
       <c r="X22" s="3"/>
     </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>127</v>
       </c>
@@ -5674,7 +5685,7 @@
       <c r="W23" s="3"/>
       <c r="X23" s="3"/>
     </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>133</v>
       </c>
@@ -5807,7 +5818,7 @@
       <c r="W25" s="3"/>
       <c r="X25" s="3"/>
     </row>
-    <row r="26" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>147</v>
       </c>
@@ -5867,7 +5878,7 @@
       <c r="W26" s="3"/>
       <c r="X26" s="3"/>
     </row>
-    <row r="27" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>150</v>
       </c>
@@ -5932,7 +5943,7 @@
       <c r="Z27" s="3"/>
       <c r="AA27" s="3"/>
     </row>
-    <row r="28" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>151</v>
       </c>
@@ -5999,7 +6010,7 @@
       <c r="Z28" s="3"/>
       <c r="AA28" s="3"/>
     </row>
-    <row r="29" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>200</v>
       </c>
@@ -6061,7 +6072,7 @@
       <c r="W29" s="3"/>
       <c r="X29" s="3"/>
     </row>
-    <row r="30" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>202</v>
       </c>
@@ -6119,7 +6130,7 @@
       <c r="W30" s="3"/>
       <c r="X30" s="3"/>
     </row>
-    <row r="31" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>206</v>
       </c>
@@ -6177,7 +6188,7 @@
       <c r="W31" s="3"/>
       <c r="X31" s="3"/>
     </row>
-    <row r="32" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>216</v>
       </c>
@@ -6251,7 +6262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>216</v>
       </c>
@@ -6325,7 +6336,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>216</v>
       </c>
@@ -6399,7 +6410,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="35" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>216</v>
       </c>
@@ -6473,7 +6484,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="36" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>216</v>
       </c>
@@ -6547,7 +6558,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="37" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>216</v>
       </c>
@@ -6621,7 +6632,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="38" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>216</v>
       </c>
@@ -6759,7 +6770,7 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
     </row>
-    <row r="40" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>221</v>
       </c>
@@ -6833,7 +6844,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="41" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>221</v>
       </c>
@@ -6907,7 +6918,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="42" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>221</v>
       </c>
@@ -6981,7 +6992,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="43" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>221</v>
       </c>
@@ -7055,7 +7066,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="44" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>221</v>
       </c>
@@ -7129,7 +7140,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="45" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>221</v>
       </c>
@@ -7277,7 +7288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>222</v>
       </c>
@@ -7351,7 +7362,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="48" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>223</v>
       </c>
@@ -7425,7 +7436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>223</v>
       </c>
@@ -7499,7 +7510,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="50" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>223</v>
       </c>
@@ -7573,7 +7584,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="51" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>224</v>
       </c>
@@ -7633,7 +7644,7 @@
       <c r="W51" s="3"/>
       <c r="X51" s="3"/>
     </row>
-    <row r="52" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>224</v>
       </c>
@@ -7707,7 +7718,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="53" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>224</v>
       </c>
@@ -7781,7 +7792,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="54" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>224</v>
       </c>
@@ -7855,7 +7866,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="55" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>224</v>
       </c>
@@ -7927,7 +7938,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="56" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>224</v>
       </c>
@@ -8001,7 +8012,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="57" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>224</v>
       </c>
@@ -8075,7 +8086,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="58" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>226</v>
       </c>
@@ -8147,7 +8158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>226</v>
       </c>
@@ -8221,7 +8232,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="60" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>226</v>
       </c>
@@ -8295,7 +8306,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="61" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>226</v>
       </c>
@@ -8369,7 +8380,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="62" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>226</v>
       </c>
@@ -8443,7 +8454,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="63" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>226</v>
       </c>
@@ -8517,7 +8528,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="64" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>226</v>
       </c>
@@ -8591,7 +8602,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="65" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>227</v>
       </c>
@@ -8663,7 +8674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>227</v>
       </c>
@@ -8737,7 +8748,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="67" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>227</v>
       </c>
@@ -8807,7 +8818,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="68" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>227</v>
       </c>
@@ -8881,7 +8892,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="69" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>227</v>
       </c>
@@ -8951,7 +8962,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="70" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>227</v>
       </c>
@@ -9021,7 +9032,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="71" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>227</v>
       </c>
@@ -9095,7 +9106,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="72" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>228</v>
       </c>
@@ -9167,7 +9178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>228</v>
       </c>
@@ -9241,7 +9252,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="74" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>228</v>
       </c>
@@ -9315,7 +9326,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="75" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>228</v>
       </c>
@@ -9389,7 +9400,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="76" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>228</v>
       </c>
@@ -9463,7 +9474,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="77" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>228</v>
       </c>
@@ -9537,7 +9548,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="78" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>228</v>
       </c>
@@ -9611,7 +9622,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="79" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
         <v>235</v>
       </c>
@@ -9670,7 +9681,7 @@
       <c r="Z79" s="3"/>
       <c r="AA79" s="3"/>
     </row>
-    <row r="80" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
         <v>236</v>
       </c>
@@ -9728,7 +9739,7 @@
       <c r="W80" s="3"/>
       <c r="X80" s="3"/>
     </row>
-    <row r="81" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
         <v>244</v>
       </c>
@@ -9796,7 +9807,7 @@
       <c r="W81" s="3"/>
       <c r="X81" s="3"/>
     </row>
-    <row r="82" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
         <v>255</v>
       </c>
@@ -9858,7 +9869,7 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
     </row>
-    <row r="83" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>255</v>
       </c>
@@ -9932,7 +9943,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="84" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>255</v>
       </c>
@@ -10006,7 +10017,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="85" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>255</v>
       </c>
@@ -10080,7 +10091,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="86" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>255</v>
       </c>
@@ -10154,7 +10165,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="87" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>255</v>
       </c>
@@ -10228,7 +10239,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="88" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>255</v>
       </c>
@@ -10302,7 +10313,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="89" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
         <v>272</v>
       </c>
@@ -10364,7 +10375,7 @@
       <c r="W89" s="3"/>
       <c r="X89" s="3"/>
     </row>
-    <row r="90" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" s="1">
         <v>288</v>
       </c>
@@ -10425,7 +10436,7 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
     </row>
-    <row r="91" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
         <v>318</v>
       </c>
@@ -10483,7 +10494,7 @@
       <c r="W91" s="3"/>
       <c r="X91" s="3"/>
     </row>
-    <row r="92" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" s="1">
         <v>326</v>
       </c>
@@ -10541,7 +10552,7 @@
       <c r="W92" s="3"/>
       <c r="X92" s="3"/>
     </row>
-    <row r="93" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" s="1">
         <v>334</v>
       </c>
@@ -10601,7 +10612,7 @@
       <c r="W93" s="3"/>
       <c r="X93" s="3"/>
     </row>
-    <row r="94" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" s="1">
         <v>336</v>
       </c>
@@ -10659,7 +10670,7 @@
       <c r="W94" s="3"/>
       <c r="X94" s="3"/>
     </row>
-    <row r="95" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" s="1">
         <v>339</v>
       </c>
@@ -10717,7 +10728,7 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
     </row>
-    <row r="96" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" s="1">
         <v>346</v>
       </c>
@@ -10775,7 +10786,7 @@
       <c r="W96" s="3"/>
       <c r="X96" s="3"/>
     </row>
-    <row r="97" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" s="1">
         <v>355</v>
       </c>
@@ -10833,7 +10844,7 @@
       <c r="W97" s="3"/>
       <c r="X97" s="3"/>
     </row>
-    <row r="98" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
         <v>361</v>
       </c>
@@ -10891,7 +10902,7 @@
       <c r="W98" s="3"/>
       <c r="X98" s="3"/>
     </row>
-    <row r="99" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
         <v>366</v>
       </c>
@@ -11007,7 +11018,7 @@
       <c r="W100" s="3"/>
       <c r="X100" s="3"/>
     </row>
-    <row r="101" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
         <v>377</v>
       </c>
@@ -11065,7 +11076,7 @@
       <c r="W101" s="3"/>
       <c r="X101" s="3"/>
     </row>
-    <row r="102" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" s="1">
         <v>392</v>
       </c>
@@ -11123,7 +11134,7 @@
       <c r="W102" s="3"/>
       <c r="X102" s="3"/>
     </row>
-    <row r="103" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" s="1">
         <v>393</v>
       </c>
@@ -11179,7 +11190,7 @@
       <c r="W103" s="3"/>
       <c r="X103" s="3"/>
     </row>
-    <row r="104" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" s="1">
         <v>402</v>
       </c>
@@ -11235,7 +11246,7 @@
       <c r="W104" s="3"/>
       <c r="X104" s="3"/>
     </row>
-    <row r="105" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" s="1">
         <v>413</v>
       </c>
@@ -11293,7 +11304,7 @@
       <c r="W105" s="3"/>
       <c r="X105" s="3"/>
     </row>
-    <row r="106" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" s="1">
         <v>423</v>
       </c>
@@ -11351,7 +11362,7 @@
       <c r="W106" s="3"/>
       <c r="X106" s="3"/>
     </row>
-    <row r="107" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" s="1">
         <v>424</v>
       </c>
@@ -11409,7 +11420,7 @@
       <c r="W107" s="3"/>
       <c r="X107" s="3"/>
     </row>
-    <row r="108" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" s="1">
         <v>437</v>
       </c>
@@ -11467,7 +11478,7 @@
       <c r="W108" s="3"/>
       <c r="X108" s="3"/>
     </row>
-    <row r="109" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" s="1">
         <v>460</v>
       </c>
@@ -11523,7 +11534,7 @@
       <c r="W109" s="3"/>
       <c r="X109" s="3"/>
     </row>
-    <row r="110" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" s="1">
         <v>487</v>
       </c>
@@ -11579,7 +11590,7 @@
       <c r="W110" s="3"/>
       <c r="X110" s="3"/>
     </row>
-    <row r="111" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" s="1">
         <v>490</v>
       </c>
@@ -11635,7 +11646,7 @@
       <c r="W111" s="3"/>
       <c r="X111" s="3"/>
     </row>
-    <row r="112" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" s="1">
         <v>491</v>
       </c>
@@ -11691,7 +11702,7 @@
       <c r="W112" s="3"/>
       <c r="X112" s="3"/>
     </row>
-    <row r="113" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" s="1">
         <v>492</v>
       </c>
@@ -11747,7 +11758,7 @@
       <c r="W113" s="3"/>
       <c r="X113" s="3"/>
     </row>
-    <row r="114" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" s="1">
         <v>493</v>
       </c>
@@ -11803,7 +11814,7 @@
       <c r="W114" s="3"/>
       <c r="X114" s="3"/>
     </row>
-    <row r="115" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" s="1">
         <v>494</v>
       </c>
@@ -11915,7 +11926,7 @@
       <c r="W116" s="3"/>
       <c r="X116" s="3"/>
     </row>
-    <row r="117" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" s="1">
         <v>496</v>
       </c>
@@ -11971,7 +11982,7 @@
       <c r="W117" s="3"/>
       <c r="X117" s="3"/>
     </row>
-    <row r="118" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" s="1">
         <v>498</v>
       </c>
@@ -12027,7 +12038,7 @@
       <c r="W118" s="3"/>
       <c r="X118" s="3"/>
     </row>
-    <row r="119" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" s="1">
         <v>499</v>
       </c>
@@ -12083,7 +12094,7 @@
       <c r="W119" s="3"/>
       <c r="X119" s="3"/>
     </row>
-    <row r="120" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" s="1">
         <v>500</v>
       </c>
@@ -12139,7 +12150,7 @@
       <c r="W120" s="3"/>
       <c r="X120" s="3"/>
     </row>
-    <row r="121" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" s="1">
         <v>501</v>
       </c>
@@ -12195,7 +12206,7 @@
       <c r="W121" s="3"/>
       <c r="X121" s="3"/>
     </row>
-    <row r="122" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" s="1">
         <v>502</v>
       </c>
@@ -12251,7 +12262,7 @@
       <c r="W122" s="3"/>
       <c r="X122" s="3"/>
     </row>
-    <row r="123" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" s="1">
         <v>503</v>
       </c>
@@ -12307,7 +12318,7 @@
       <c r="W123" s="3"/>
       <c r="X123" s="3"/>
     </row>
-    <row r="124" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" s="1">
         <v>504</v>
       </c>
@@ -12363,7 +12374,7 @@
       <c r="W124" s="3"/>
       <c r="X124" s="3"/>
     </row>
-    <row r="125" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" s="1">
         <v>505</v>
       </c>
@@ -12419,7 +12430,7 @@
       <c r="W125" s="3"/>
       <c r="X125" s="3"/>
     </row>
-    <row r="126" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" s="1">
         <v>508</v>
       </c>
@@ -12475,7 +12486,7 @@
       <c r="W126" s="3"/>
       <c r="X126" s="3"/>
     </row>
-    <row r="127" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" s="1">
         <v>522</v>
       </c>
@@ -12529,7 +12540,7 @@
       <c r="W127" s="3"/>
       <c r="X127" s="3"/>
     </row>
-    <row r="128" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" s="1">
         <v>527</v>
       </c>
@@ -12583,7 +12594,7 @@
       <c r="W128" s="3"/>
       <c r="X128" s="3"/>
     </row>
-    <row r="129" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" s="1">
         <v>528</v>
       </c>
@@ -12640,7 +12651,7 @@
       <c r="Z129" s="3"/>
       <c r="AA129" s="3"/>
     </row>
-    <row r="130" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" s="1">
         <v>541</v>
       </c>
@@ -12694,7 +12705,7 @@
       <c r="W130" s="3"/>
       <c r="X130" s="3"/>
     </row>
-    <row r="131" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" s="1">
         <v>542</v>
       </c>
@@ -12758,7 +12769,7 @@
       <c r="W131" s="3"/>
       <c r="X131" s="3"/>
     </row>
-    <row r="132" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>542</v>
       </c>
@@ -12832,7 +12843,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="133" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>542</v>
       </c>
@@ -12906,7 +12917,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="134" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>542</v>
       </c>
@@ -12980,7 +12991,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="135" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>542</v>
       </c>
@@ -13054,7 +13065,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="136" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" s="1">
         <v>546</v>
       </c>
@@ -13116,7 +13127,7 @@
       <c r="W136" s="3"/>
       <c r="X136" s="3"/>
     </row>
-    <row r="137" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137">
         <v>546</v>
       </c>
@@ -13187,7 +13198,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="138" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>546</v>
       </c>
@@ -13258,7 +13269,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="139" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>546</v>
       </c>
@@ -13329,7 +13340,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="140" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" s="1">
         <v>547</v>
       </c>
@@ -13383,7 +13394,7 @@
       <c r="W140" s="3"/>
       <c r="X140" s="3"/>
     </row>
-    <row r="141" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" s="1">
         <v>552</v>
       </c>
@@ -13437,7 +13448,7 @@
       <c r="W141" s="3"/>
       <c r="X141" s="3"/>
     </row>
-    <row r="142" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" s="1">
         <v>553</v>
       </c>
@@ -13491,7 +13502,7 @@
       <c r="W142" s="3"/>
       <c r="X142" s="3"/>
     </row>
-    <row r="143" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" s="1">
         <v>556</v>
       </c>
@@ -13545,7 +13556,7 @@
       <c r="W143" s="3"/>
       <c r="X143" s="3"/>
     </row>
-    <row r="144" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" s="1">
         <v>290</v>
       </c>
@@ -13622,7 +13633,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="145" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145">
         <v>290</v>
       </c>
@@ -13702,7 +13713,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="146" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>290</v>
       </c>
@@ -13782,7 +13793,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="147" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>290</v>
       </c>
@@ -13862,7 +13873,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="148" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>290</v>
       </c>
@@ -13942,7 +13953,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="149" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>290</v>
       </c>
@@ -14022,7 +14033,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="150" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>290</v>
       </c>
@@ -14102,7 +14113,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="151" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151">
         <v>290</v>
       </c>
@@ -14182,7 +14193,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="152" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>290</v>
       </c>
@@ -14262,7 +14273,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="153" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153">
         <v>290</v>
       </c>
@@ -14342,7 +14353,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="154" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" s="1">
         <v>77</v>
       </c>
@@ -14419,7 +14430,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="155" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" s="1">
         <v>121</v>
       </c>
@@ -14573,7 +14584,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="157" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" s="1">
         <v>124</v>
       </c>
@@ -14650,7 +14661,7 @@
         <v>9.1157702825888781E-2</v>
       </c>
     </row>
-    <row r="158" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" s="1">
         <v>125</v>
       </c>
@@ -14727,7 +14738,7 @@
         <v>0.27347310847766643</v>
       </c>
     </row>
-    <row r="159" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" s="1">
         <v>128</v>
       </c>
@@ -14804,7 +14815,7 @@
         <v>0.86</v>
       </c>
     </row>
-    <row r="160" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" s="1">
         <v>172</v>
       </c>
@@ -14881,7 +14892,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="161" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" s="1">
         <v>208</v>
       </c>
@@ -14958,7 +14969,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="162" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162">
         <v>208</v>
       </c>
@@ -15035,7 +15046,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="163" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163">
         <v>208</v>
       </c>
@@ -15112,7 +15123,7 @@
         <v>249.5</v>
       </c>
     </row>
-    <row r="164" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164">
         <v>208</v>
       </c>
@@ -15189,7 +15200,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="165" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165">
         <v>208</v>
       </c>
@@ -15266,7 +15277,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="166" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166">
         <v>208</v>
       </c>
@@ -15343,7 +15354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167">
         <v>208</v>
       </c>
@@ -15420,7 +15431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" s="1">
         <v>214</v>
       </c>
@@ -15497,7 +15508,7 @@
         <v>2054.7600000000002</v>
       </c>
     </row>
-    <row r="169" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169">
         <v>214</v>
       </c>
@@ -15574,7 +15585,7 @@
         <v>1130.94</v>
       </c>
     </row>
-    <row r="170" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170">
         <v>214</v>
       </c>
@@ -15651,7 +15662,7 @@
         <v>406.56</v>
       </c>
     </row>
-    <row r="171" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171">
         <v>214</v>
       </c>
@@ -15728,7 +15739,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="172" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172">
         <v>214</v>
       </c>
@@ -15805,7 +15816,7 @@
         <v>406.9</v>
       </c>
     </row>
-    <row r="173" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173">
         <v>214</v>
       </c>
@@ -15882,7 +15893,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="174" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174">
         <v>214</v>
       </c>
@@ -15959,7 +15970,7 @@
         <v>110.36</v>
       </c>
     </row>
-    <row r="175" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" s="1">
         <v>217</v>
       </c>
@@ -16036,7 +16047,7 @@
         <v>139.19</v>
       </c>
     </row>
-    <row r="176" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176">
         <v>217</v>
       </c>
@@ -16113,7 +16124,7 @@
         <v>240.68</v>
       </c>
     </row>
-    <row r="177" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177">
         <v>217</v>
       </c>
@@ -16190,7 +16201,7 @@
         <v>19.850000000000001</v>
       </c>
     </row>
-    <row r="178" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178">
         <v>217</v>
       </c>
@@ -16267,7 +16278,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="179" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179">
         <v>217</v>
       </c>
@@ -16344,7 +16355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180">
         <v>217</v>
       </c>
@@ -16421,7 +16432,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="181" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181">
         <v>217</v>
       </c>
@@ -16498,7 +16509,7 @@
         <v>51.96</v>
       </c>
     </row>
-    <row r="182" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" s="1">
         <v>218</v>
       </c>
@@ -16575,7 +16586,7 @@
         <v>113367.97</v>
       </c>
     </row>
-    <row r="183" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183">
         <v>218</v>
       </c>
@@ -16652,7 +16663,7 @@
         <v>54501</v>
       </c>
     </row>
-    <row r="184" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184">
         <v>218</v>
       </c>
@@ -16729,7 +16740,7 @@
         <v>42180</v>
       </c>
     </row>
-    <row r="185" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185">
         <v>218</v>
       </c>
@@ -16806,7 +16817,7 @@
         <v>3600</v>
       </c>
     </row>
-    <row r="186" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186">
         <v>218</v>
       </c>
@@ -16883,7 +16894,7 @@
         <v>10775</v>
       </c>
     </row>
-    <row r="187" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187">
         <v>218</v>
       </c>
@@ -16960,7 +16971,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="188" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188">
         <v>218</v>
       </c>
@@ -17037,7 +17048,7 @@
         <v>1712</v>
       </c>
     </row>
-    <row r="189" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" s="1">
         <v>225</v>
       </c>
@@ -17114,7 +17125,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="190" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190">
         <v>225</v>
       </c>
@@ -17191,7 +17202,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="191" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191">
         <v>225</v>
       </c>
@@ -17266,7 +17277,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="192" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192">
         <v>225</v>
       </c>
@@ -17343,7 +17354,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="193" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193">
         <v>225</v>
       </c>
@@ -17420,7 +17431,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="194" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194">
         <v>225</v>
       </c>
@@ -17497,7 +17508,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="195" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195">
         <v>225</v>
       </c>
@@ -17574,7 +17585,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="196" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" s="1">
         <v>239</v>
       </c>
@@ -17651,7 +17662,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="197" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197">
         <v>239</v>
       </c>
@@ -17728,7 +17739,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="198" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198">
         <v>239</v>
       </c>
@@ -17805,7 +17816,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="199" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199">
         <v>239</v>
       </c>
@@ -17880,7 +17891,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="200" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200">
         <v>239</v>
       </c>
@@ -17957,7 +17968,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="201" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201">
         <v>239</v>
       </c>
@@ -18034,7 +18045,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="202" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" s="1">
         <v>241</v>
       </c>
@@ -18186,7 +18197,7 @@
         <v>2072.4699999999998</v>
       </c>
     </row>
-    <row r="204" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204">
         <v>434</v>
       </c>
@@ -18263,7 +18274,7 @@
         <v>2071.7199999999998</v>
       </c>
     </row>
-    <row r="205" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205">
         <v>434</v>
       </c>
@@ -18340,7 +18351,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="206" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206">
         <v>434</v>
       </c>
@@ -18417,7 +18428,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="207" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207">
         <v>434</v>
       </c>
@@ -18494,7 +18505,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208">
         <v>434</v>
       </c>
@@ -18571,7 +18582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209">
         <v>434</v>
       </c>
@@ -18648,7 +18659,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="210" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" s="1">
         <v>436</v>
       </c>
@@ -18725,7 +18736,7 @@
         <v>9.1999999999999993</v>
       </c>
     </row>
-    <row r="211" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211">
         <v>436</v>
       </c>
@@ -18802,7 +18813,7 @@
         <v>6.1</v>
       </c>
     </row>
-    <row r="212" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212">
         <v>436</v>
       </c>
@@ -18879,7 +18890,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="213" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213" s="1">
         <v>485</v>
       </c>
@@ -18952,7 +18963,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="214" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214">
         <v>485</v>
       </c>
@@ -19024,7 +19035,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="215" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215">
         <v>485</v>
       </c>
@@ -19098,7 +19109,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="216" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216">
         <v>485</v>
       </c>
@@ -19172,7 +19183,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="217" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217">
         <v>485</v>
       </c>
@@ -19246,7 +19257,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="218" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218">
         <v>485</v>
       </c>
@@ -19320,7 +19331,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="219" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219">
         <v>485</v>
       </c>
@@ -19394,7 +19405,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="220" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220">
         <v>485</v>
       </c>
@@ -19468,7 +19479,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="221" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221">
         <v>485</v>
       </c>
@@ -19542,7 +19553,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="222" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222">
         <v>485</v>
       </c>
@@ -19616,7 +19627,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="223" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223" s="1">
         <v>488</v>
       </c>
@@ -19691,7 +19702,7 @@
         <v>78.048780487804876</v>
       </c>
     </row>
-    <row r="224" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224">
         <v>488</v>
       </c>
@@ -19765,7 +19776,7 @@
         <v>78.790000000000006</v>
       </c>
     </row>
-    <row r="225" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225">
         <v>488</v>
       </c>
@@ -19839,7 +19850,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="226" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226">
         <v>488</v>
       </c>
@@ -19913,7 +19924,7 @@
         <v>82.61</v>
       </c>
     </row>
-    <row r="227" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227">
         <v>488</v>
       </c>
@@ -19987,7 +19998,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="228" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228">
         <v>488</v>
       </c>
@@ -20061,7 +20072,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="229" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229">
         <v>488</v>
       </c>
@@ -20135,7 +20146,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="230" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230">
         <v>488</v>
       </c>
@@ -20209,7 +20220,7 @@
         <v>79.03</v>
       </c>
     </row>
-    <row r="231" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231">
         <v>488</v>
       </c>
@@ -20283,7 +20294,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="232" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232">
         <v>488</v>
       </c>
@@ -20357,7 +20368,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="233" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233" s="1">
         <v>509</v>
       </c>
@@ -20422,7 +20433,7 @@
         <v>99.45</v>
       </c>
     </row>
-    <row r="234" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234">
         <v>509</v>
       </c>
@@ -20496,7 +20507,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="235" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235">
         <v>509</v>
       </c>
@@ -20570,7 +20581,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="236" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236">
         <v>509</v>
       </c>
@@ -20644,7 +20655,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="237" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237">
         <v>509</v>
       </c>
@@ -20718,7 +20729,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="238" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238">
         <v>509</v>
       </c>
@@ -20792,7 +20803,7 @@
         <v>98.77</v>
       </c>
     </row>
-    <row r="239" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239">
         <v>509</v>
       </c>
@@ -20866,7 +20877,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="240" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A240">
         <v>509</v>
       </c>
@@ -20940,7 +20951,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="241" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A241">
         <v>509</v>
       </c>
@@ -21014,7 +21025,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="242" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242">
         <v>509</v>
       </c>
@@ -21088,7 +21099,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="243" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243">
         <v>509</v>
       </c>
@@ -21162,7 +21173,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="244" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244">
         <v>509</v>
       </c>
@@ -21236,7 +21247,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="245" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A245">
         <v>509</v>
       </c>
@@ -21310,7 +21321,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="246" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246">
         <v>509</v>
       </c>
@@ -21384,7 +21395,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="247" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247">
         <v>509</v>
       </c>
@@ -21458,7 +21469,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="248" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248">
         <v>509</v>
       </c>
@@ -21532,7 +21543,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="249" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249">
         <v>509</v>
       </c>
@@ -21606,7 +21617,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="250" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A250">
         <v>509</v>
       </c>
@@ -21680,7 +21691,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="251" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251">
         <v>509</v>
       </c>
@@ -21754,7 +21765,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="252" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A252" s="1">
         <v>68</v>
       </c>
@@ -21835,7 +21846,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="253" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A253" s="1">
         <v>73</v>
       </c>
@@ -21918,7 +21929,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="254" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A254" s="1">
         <v>74</v>
       </c>
@@ -22001,7 +22012,7 @@
         <v>83.098591549295776</v>
       </c>
     </row>
-    <row r="255" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A255" s="1">
         <v>86</v>
       </c>
@@ -22084,7 +22095,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="256" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A256" s="1">
         <v>95</v>
       </c>
@@ -22167,7 +22178,7 @@
         <v>86.486486486486484</v>
       </c>
     </row>
-    <row r="257" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A257" s="1">
         <v>143</v>
       </c>
@@ -22246,7 +22257,7 @@
       <c r="Z257" s="3"/>
       <c r="AA257" s="3"/>
     </row>
-    <row r="258" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A258" s="1">
         <v>145</v>
       </c>
@@ -22325,7 +22336,7 @@
       <c r="Z258" s="3"/>
       <c r="AA258" s="3"/>
     </row>
-    <row r="259" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A259" s="1">
         <v>146</v>
       </c>
@@ -22404,7 +22415,7 @@
       <c r="Z259" s="3"/>
       <c r="AA259" s="3"/>
     </row>
-    <row r="260" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A260" s="1">
         <v>148</v>
       </c>
@@ -22483,7 +22494,7 @@
       <c r="Z260" s="3"/>
       <c r="AA260" s="3"/>
     </row>
-    <row r="261" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A261" s="1">
         <v>159</v>
       </c>
@@ -22533,7 +22544,7 @@
         <v>97.8</v>
       </c>
     </row>
-    <row r="262" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A262" s="1">
         <v>167</v>
       </c>
@@ -22606,7 +22617,7 @@
       <c r="Z262" s="3"/>
       <c r="AA262" s="3"/>
     </row>
-    <row r="263" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A263" s="1">
         <v>193</v>
       </c>
@@ -22673,7 +22684,7 @@
       <c r="Z263" s="3"/>
       <c r="AA263" s="3"/>
     </row>
-    <row r="264" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A264" s="1">
         <v>199</v>
       </c>
@@ -22744,7 +22755,7 @@
       <c r="Z264" s="3"/>
       <c r="AA264" s="3"/>
     </row>
-    <row r="265" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A265" s="1">
         <v>203</v>
       </c>
@@ -22823,7 +22834,7 @@
       <c r="Z265" s="3"/>
       <c r="AA265" s="3"/>
     </row>
-    <row r="266" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A266">
         <v>203</v>
       </c>
@@ -22906,7 +22917,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="267" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A267">
         <v>203</v>
       </c>
@@ -22989,7 +23000,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="268" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A268">
         <v>203</v>
       </c>
@@ -23072,7 +23083,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="269" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A269" s="1">
         <v>204</v>
       </c>
@@ -23139,7 +23150,7 @@
       <c r="Z269" s="3"/>
       <c r="AA269" s="3"/>
     </row>
-    <row r="270" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A270" s="1">
         <v>205</v>
       </c>
@@ -23206,7 +23217,7 @@
       <c r="Z270" s="3"/>
       <c r="AA270" s="3"/>
     </row>
-    <row r="271" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A271" s="1">
         <v>207</v>
       </c>
@@ -23352,7 +23363,7 @@
       <c r="Z272" s="3"/>
       <c r="AA272" s="3"/>
     </row>
-    <row r="273" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A273">
         <v>215</v>
       </c>
@@ -23435,7 +23446,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="274" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A274">
         <v>215</v>
       </c>
@@ -23518,7 +23529,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="275" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A275">
         <v>215</v>
       </c>
@@ -23601,7 +23612,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="276" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A276">
         <v>215</v>
       </c>
@@ -23684,7 +23695,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="277" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A277">
         <v>215</v>
       </c>
@@ -23767,7 +23778,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="278" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A278">
         <v>215</v>
       </c>
@@ -23927,7 +23938,7 @@
       <c r="Z279" s="3"/>
       <c r="AA279" s="3"/>
     </row>
-    <row r="280" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A280">
         <v>219</v>
       </c>
@@ -24010,7 +24021,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="281" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A281">
         <v>219</v>
       </c>
@@ -24093,7 +24104,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="282" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A282">
         <v>219</v>
       </c>
@@ -24176,7 +24187,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="283" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A283">
         <v>219</v>
       </c>
@@ -24259,7 +24270,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="284" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A284">
         <v>219</v>
       </c>
@@ -24342,7 +24353,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="285" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A285">
         <v>219</v>
       </c>
@@ -24425,7 +24436,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="286" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A286">
         <v>219</v>
       </c>
@@ -24566,7 +24577,7 @@
       <c r="Z287" s="3"/>
       <c r="AA287" s="3"/>
     </row>
-    <row r="288" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A288">
         <v>220</v>
       </c>
@@ -24649,7 +24660,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="289" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A289">
         <v>220</v>
       </c>
@@ -24732,7 +24743,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="290" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A290">
         <v>220</v>
       </c>
@@ -24815,7 +24826,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="291" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A291">
         <v>220</v>
       </c>
@@ -24898,7 +24909,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="292" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A292">
         <v>220</v>
       </c>
@@ -24977,7 +24988,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="293" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A293">
         <v>220</v>
       </c>
@@ -25060,7 +25071,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="294" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A294" s="1">
         <v>230</v>
       </c>
@@ -25127,7 +25138,7 @@
       <c r="Z294" s="3"/>
       <c r="AA294" s="3"/>
     </row>
-    <row r="295" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A295" s="1">
         <v>231</v>
       </c>
@@ -25194,7 +25205,7 @@
       <c r="Z295" s="3"/>
       <c r="AA295" s="3"/>
     </row>
-    <row r="296" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A296" s="1">
         <v>232</v>
       </c>
@@ -25261,7 +25272,7 @@
       <c r="Z296" s="3"/>
       <c r="AA296" s="3"/>
     </row>
-    <row r="297" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A297" s="1">
         <v>245</v>
       </c>
@@ -25328,7 +25339,7 @@
       <c r="Z297" s="3"/>
       <c r="AA297" s="3"/>
     </row>
-    <row r="298" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A298" s="1">
         <v>246</v>
       </c>
@@ -25393,7 +25404,7 @@
       <c r="Z298" s="3"/>
       <c r="AA298" s="3"/>
     </row>
-    <row r="299" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A299" s="1">
         <v>252</v>
       </c>
@@ -25460,7 +25471,7 @@
       <c r="Z299" s="3"/>
       <c r="AA299" s="3"/>
     </row>
-    <row r="300" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A300" s="1">
         <v>256</v>
       </c>
@@ -25527,7 +25538,7 @@
       <c r="Z300" s="3"/>
       <c r="AA300" s="3"/>
     </row>
-    <row r="301" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A301" s="1">
         <v>260</v>
       </c>
@@ -25594,7 +25605,7 @@
       <c r="Z301" s="3"/>
       <c r="AA301" s="3"/>
     </row>
-    <row r="302" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A302" s="1">
         <v>261</v>
       </c>
@@ -25661,7 +25672,7 @@
       <c r="Z302" s="3"/>
       <c r="AA302" s="3"/>
     </row>
-    <row r="303" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A303" s="1">
         <v>262</v>
       </c>
@@ -25726,7 +25737,7 @@
       <c r="Z303" s="3"/>
       <c r="AA303" s="3"/>
     </row>
-    <row r="304" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A304" s="1">
         <v>268</v>
       </c>
@@ -25793,7 +25804,7 @@
       <c r="Z304" s="3"/>
       <c r="AA304" s="3"/>
     </row>
-    <row r="305" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A305" s="1">
         <v>269</v>
       </c>
@@ -25860,7 +25871,7 @@
       <c r="Z305" s="3"/>
       <c r="AA305" s="3"/>
     </row>
-    <row r="306" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A306" s="1">
         <v>270</v>
       </c>
@@ -25927,7 +25938,7 @@
       <c r="Z306" s="3"/>
       <c r="AA306" s="3"/>
     </row>
-    <row r="307" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A307" s="1">
         <v>271</v>
       </c>
@@ -25994,7 +26005,7 @@
       <c r="Z307" s="3"/>
       <c r="AA307" s="3"/>
     </row>
-    <row r="308" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A308" s="1">
         <v>273</v>
       </c>
@@ -26061,7 +26072,7 @@
       <c r="Z308" s="3"/>
       <c r="AA308" s="3"/>
     </row>
-    <row r="309" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A309" s="1">
         <v>274</v>
       </c>
@@ -26140,7 +26151,7 @@
       <c r="Z309" s="3"/>
       <c r="AA309" s="3"/>
     </row>
-    <row r="310" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A310">
         <v>274</v>
       </c>
@@ -26223,7 +26234,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="311" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A311">
         <v>274</v>
       </c>
@@ -26306,7 +26317,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="312" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A312">
         <v>274</v>
       </c>
@@ -26389,7 +26400,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="313" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A313">
         <v>274</v>
       </c>
@@ -26472,7 +26483,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="314" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A314" s="1">
         <v>275</v>
       </c>
@@ -26553,7 +26564,7 @@
       </c>
       <c r="AA314" s="3"/>
     </row>
-    <row r="315" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A315">
         <v>275</v>
       </c>
@@ -26636,7 +26647,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="316" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A316">
         <v>275</v>
       </c>
@@ -26719,7 +26730,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="317" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A317">
         <v>275</v>
       </c>
@@ -26802,7 +26813,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="318" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A318" s="1">
         <v>276</v>
       </c>
@@ -26869,7 +26880,7 @@
       <c r="Z318" s="3"/>
       <c r="AA318" s="3"/>
     </row>
-    <row r="319" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A319" s="1">
         <v>277</v>
       </c>
@@ -26936,7 +26947,7 @@
       <c r="Z319" s="3"/>
       <c r="AA319" s="3"/>
     </row>
-    <row r="320" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A320" s="1">
         <v>278</v>
       </c>
@@ -27019,7 +27030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="321" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A321">
         <v>278</v>
       </c>
@@ -27102,7 +27113,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="322" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A322">
         <v>278</v>
       </c>
@@ -27185,7 +27196,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="323" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A323">
         <v>278</v>
       </c>
@@ -27268,7 +27279,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="324" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A324" s="1">
         <v>282</v>
       </c>
@@ -27335,7 +27346,7 @@
       <c r="Z324" s="3"/>
       <c r="AA324" s="3"/>
     </row>
-    <row r="325" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A325" s="1">
         <v>283</v>
       </c>
@@ -27402,7 +27413,7 @@
       <c r="Z325" s="3"/>
       <c r="AA325" s="3"/>
     </row>
-    <row r="326" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A326" s="1">
         <v>285</v>
       </c>
@@ -27469,7 +27480,7 @@
       <c r="Z326" s="3"/>
       <c r="AA326" s="3"/>
     </row>
-    <row r="327" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A327" s="1">
         <v>286</v>
       </c>
@@ -27552,7 +27563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="328" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A328">
         <v>286</v>
       </c>
@@ -27635,7 +27646,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="329" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A329">
         <v>286</v>
       </c>
@@ -27718,7 +27729,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="330" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A330">
         <v>286</v>
       </c>
@@ -27801,7 +27812,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="331" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A331">
         <v>286</v>
       </c>
@@ -27884,7 +27895,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="332" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A332" s="1">
         <v>292</v>
       </c>
@@ -27963,7 +27974,7 @@
       <c r="Z332" s="3"/>
       <c r="AA332" s="3"/>
     </row>
-    <row r="333" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A333">
         <v>292</v>
       </c>
@@ -28046,7 +28057,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="334" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A334">
         <v>292</v>
       </c>
@@ -28129,7 +28140,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="335" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A335">
         <v>292</v>
       </c>
@@ -28291,7 +28302,7 @@
       <c r="Z336" s="3"/>
       <c r="AA336" s="3"/>
     </row>
-    <row r="337" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A337">
         <v>294</v>
       </c>
@@ -28374,7 +28385,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="338" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A338">
         <v>294</v>
       </c>
@@ -28457,7 +28468,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="339" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A339">
         <v>294</v>
       </c>
@@ -28540,7 +28551,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="340" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A340" s="1">
         <v>302</v>
       </c>
@@ -28623,7 +28634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="341" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A341">
         <v>302</v>
       </c>
@@ -28706,7 +28717,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="342" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A342">
         <v>302</v>
       </c>
@@ -28789,7 +28800,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="343" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A343">
         <v>302</v>
       </c>
@@ -28872,7 +28883,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="344" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A344">
         <v>302</v>
       </c>
@@ -28955,7 +28966,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="345" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A345" s="1">
         <v>303</v>
       </c>
@@ -29032,7 +29043,7 @@
       <c r="Z345" s="3"/>
       <c r="AA345" s="3"/>
     </row>
-    <row r="346" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A346">
         <v>303</v>
       </c>
@@ -29115,7 +29126,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="347" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A347">
         <v>303</v>
       </c>
@@ -29198,7 +29209,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="348" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A348">
         <v>303</v>
       </c>
@@ -29281,7 +29292,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="349" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A349" s="1">
         <v>304</v>
       </c>
@@ -29348,7 +29359,7 @@
       <c r="Z349" s="3"/>
       <c r="AA349" s="3"/>
     </row>
-    <row r="350" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A350" s="1">
         <v>323</v>
       </c>
@@ -29415,7 +29426,7 @@
       <c r="Z350" s="3"/>
       <c r="AA350" s="3"/>
     </row>
-    <row r="351" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A351" s="1">
         <v>324</v>
       </c>
@@ -29482,7 +29493,7 @@
       <c r="Z351" s="3"/>
       <c r="AA351" s="3"/>
     </row>
-    <row r="352" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A352" s="1">
         <v>325</v>
       </c>
@@ -29549,7 +29560,7 @@
       <c r="Z352" s="3"/>
       <c r="AA352" s="3"/>
     </row>
-    <row r="353" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A353" s="1">
         <v>327</v>
       </c>
@@ -29616,7 +29627,7 @@
       <c r="Z353" s="3"/>
       <c r="AA353" s="3"/>
     </row>
-    <row r="354" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A354" s="1">
         <v>332</v>
       </c>
@@ -29683,7 +29694,7 @@
       <c r="Z354" s="3"/>
       <c r="AA354" s="3"/>
     </row>
-    <row r="355" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A355" s="1">
         <v>337</v>
       </c>
@@ -29750,7 +29761,7 @@
       <c r="Z355" s="3"/>
       <c r="AA355" s="3"/>
     </row>
-    <row r="356" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A356" s="1">
         <v>338</v>
       </c>
@@ -29817,7 +29828,7 @@
       <c r="Z356" s="3"/>
       <c r="AA356" s="3"/>
     </row>
-    <row r="357" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A357" s="1">
         <v>341</v>
       </c>
@@ -29884,7 +29895,7 @@
       <c r="Z357" s="3"/>
       <c r="AA357" s="3"/>
     </row>
-    <row r="358" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A358" s="1">
         <v>344</v>
       </c>
@@ -29951,7 +29962,7 @@
       <c r="Z358" s="3"/>
       <c r="AA358" s="3"/>
     </row>
-    <row r="359" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A359" s="1">
         <v>356</v>
       </c>
@@ -30018,7 +30029,7 @@
       <c r="Z359" s="3"/>
       <c r="AA359" s="3"/>
     </row>
-    <row r="360" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A360" s="1">
         <v>357</v>
       </c>
@@ -30083,7 +30094,7 @@
       <c r="Z360" s="3"/>
       <c r="AA360" s="3"/>
     </row>
-    <row r="361" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A361" s="1">
         <v>358</v>
       </c>
@@ -30150,7 +30161,7 @@
       <c r="Z361" s="3"/>
       <c r="AA361" s="3"/>
     </row>
-    <row r="362" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A362" s="1">
         <v>359</v>
       </c>
@@ -30213,7 +30224,7 @@
       <c r="Z362" s="3"/>
       <c r="AA362" s="3"/>
     </row>
-    <row r="363" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A363" s="1">
         <v>362</v>
       </c>
@@ -30292,7 +30303,7 @@
       <c r="Z363" s="3"/>
       <c r="AA363" s="3"/>
     </row>
-    <row r="364" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A364">
         <v>362</v>
       </c>
@@ -30375,7 +30386,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="365" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A365">
         <v>362</v>
       </c>
@@ -30458,7 +30469,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="366" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A366" s="1">
         <v>363</v>
       </c>
@@ -30590,7 +30601,7 @@
       <c r="Z367" s="3"/>
       <c r="AA367" s="3"/>
     </row>
-    <row r="368" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A368" s="1">
         <v>369</v>
       </c>
@@ -30673,7 +30684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="369" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A369">
         <v>369</v>
       </c>
@@ -30756,7 +30767,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="370" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A370">
         <v>369</v>
       </c>
@@ -30839,7 +30850,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="371" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A371" s="1">
         <v>371</v>
       </c>
@@ -30906,7 +30917,7 @@
       <c r="Z371" s="3"/>
       <c r="AA371" s="3"/>
     </row>
-    <row r="372" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A372" s="1">
         <v>375</v>
       </c>
@@ -30989,7 +31000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="373" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A373">
         <v>375</v>
       </c>
@@ -31072,7 +31083,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="374" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A374">
         <v>375</v>
       </c>
@@ -31155,7 +31166,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="375" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A375" s="1">
         <v>376</v>
       </c>
@@ -31222,7 +31233,7 @@
       <c r="Z375" s="3"/>
       <c r="AA375" s="3"/>
     </row>
-    <row r="376" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A376" s="1">
         <v>379</v>
       </c>
@@ -31289,7 +31300,7 @@
       <c r="Z376" s="3"/>
       <c r="AA376" s="3"/>
     </row>
-    <row r="377" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A377" s="1">
         <v>381</v>
       </c>
@@ -31356,7 +31367,7 @@
       <c r="Z377" s="3"/>
       <c r="AA377" s="3"/>
     </row>
-    <row r="378" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A378" s="1">
         <v>382</v>
       </c>
@@ -31423,7 +31434,7 @@
       <c r="Z378" s="3"/>
       <c r="AA378" s="3"/>
     </row>
-    <row r="379" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A379" s="1">
         <v>383</v>
       </c>
@@ -31490,7 +31501,7 @@
       <c r="Z379" s="3"/>
       <c r="AA379" s="3"/>
     </row>
-    <row r="380" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A380" s="1">
         <v>384</v>
       </c>
@@ -31557,7 +31568,7 @@
       <c r="Z380" s="3"/>
       <c r="AA380" s="3"/>
     </row>
-    <row r="381" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A381" s="1">
         <v>385</v>
       </c>
@@ -31624,7 +31635,7 @@
       <c r="Z381" s="3"/>
       <c r="AA381" s="3"/>
     </row>
-    <row r="382" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A382" s="1">
         <v>386</v>
       </c>
@@ -31703,7 +31714,7 @@
       <c r="Z382" s="3"/>
       <c r="AA382" s="3"/>
     </row>
-    <row r="383" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A383">
         <v>386</v>
       </c>
@@ -31786,7 +31797,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="384" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A384">
         <v>386</v>
       </c>
@@ -31869,7 +31880,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="385" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A385">
         <v>386</v>
       </c>
@@ -31952,7 +31963,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="386" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A386" s="1">
         <v>389</v>
       </c>
@@ -32031,7 +32042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="387" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A387">
         <v>389</v>
       </c>
@@ -32111,7 +32122,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="388" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A388">
         <v>389</v>
       </c>
@@ -32191,7 +32202,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="389" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A389">
         <v>389</v>
       </c>
@@ -32271,7 +32282,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="390" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A390">
         <v>389</v>
       </c>
@@ -32351,7 +32362,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="391" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A391">
         <v>389</v>
       </c>
@@ -32431,7 +32442,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="392" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A392">
         <v>389</v>
       </c>
@@ -32511,7 +32522,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="393" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A393">
         <v>389</v>
       </c>
@@ -32591,7 +32602,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="394" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A394">
         <v>389</v>
       </c>
@@ -32671,7 +32682,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="395" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A395">
         <v>389</v>
       </c>
@@ -32751,7 +32762,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="396" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A396">
         <v>389</v>
       </c>
@@ -32831,7 +32842,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="397" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A397">
         <v>389</v>
       </c>
@@ -32911,7 +32922,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="398" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A398">
         <v>389</v>
       </c>
@@ -32991,7 +33002,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="399" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A399" s="1">
         <v>397</v>
       </c>
@@ -33058,7 +33069,7 @@
       <c r="Z399" s="3"/>
       <c r="AA399" s="3"/>
     </row>
-    <row r="400" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A400" s="1">
         <v>398</v>
       </c>
@@ -33125,7 +33136,7 @@
       <c r="Z400" s="3"/>
       <c r="AA400" s="3"/>
     </row>
-    <row r="401" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A401" s="1">
         <v>399</v>
       </c>
@@ -33192,7 +33203,7 @@
       <c r="Z401" s="3"/>
       <c r="AA401" s="3"/>
     </row>
-    <row r="402" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A402" s="1">
         <v>400</v>
       </c>
@@ -33259,7 +33270,7 @@
       <c r="Z402" s="3"/>
       <c r="AA402" s="3"/>
     </row>
-    <row r="403" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A403" s="1">
         <v>401</v>
       </c>
@@ -33326,7 +33337,7 @@
       <c r="Z403" s="3"/>
       <c r="AA403" s="3"/>
     </row>
-    <row r="404" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A404" s="1">
         <v>403</v>
       </c>
@@ -33393,7 +33404,7 @@
       <c r="Z404" s="3"/>
       <c r="AA404" s="3"/>
     </row>
-    <row r="405" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A405" s="1">
         <v>408</v>
       </c>
@@ -33472,7 +33483,7 @@
       <c r="Z405" s="3"/>
       <c r="AA405" s="3"/>
     </row>
-    <row r="406" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A406">
         <v>408</v>
       </c>
@@ -33555,7 +33566,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="407" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A407">
         <v>408</v>
       </c>
@@ -33638,7 +33649,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="408" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A408">
         <v>408</v>
       </c>
@@ -33721,7 +33732,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="409" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A409" s="1">
         <v>422</v>
       </c>
@@ -33788,7 +33799,7 @@
       <c r="Z409" s="3"/>
       <c r="AA409" s="3"/>
     </row>
-    <row r="410" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A410" s="1">
         <v>426</v>
       </c>
@@ -33849,7 +33860,7 @@
       <c r="Z410" s="3"/>
       <c r="AA410" s="3"/>
     </row>
-    <row r="411" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A411" s="1">
         <v>427</v>
       </c>
@@ -33932,7 +33943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="412" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A412">
         <v>427</v>
       </c>
@@ -34015,7 +34026,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="413" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A413">
         <v>427</v>
       </c>
@@ -34098,7 +34109,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="414" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A414">
         <v>427</v>
       </c>
@@ -34181,7 +34192,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="415" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A415">
         <v>427</v>
       </c>
@@ -34264,7 +34275,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="416" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A416">
         <v>427</v>
       </c>
@@ -34343,7 +34354,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="417" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A417">
         <v>427</v>
       </c>
@@ -34426,7 +34437,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="418" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A418" s="1">
         <v>428</v>
       </c>
@@ -34505,7 +34516,7 @@
       <c r="Z418" s="3"/>
       <c r="AA418" s="3"/>
     </row>
-    <row r="419" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A419">
         <v>428</v>
       </c>
@@ -34588,7 +34599,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="420" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A420">
         <v>428</v>
       </c>
@@ -34671,7 +34682,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="421" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A421">
         <v>428</v>
       </c>
@@ -34752,7 +34763,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="422" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A422">
         <v>428</v>
       </c>
@@ -34835,7 +34846,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="423" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A423">
         <v>428</v>
       </c>
@@ -34914,7 +34925,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="424" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A424">
         <v>428</v>
       </c>
@@ -34995,7 +35006,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="425" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A425">
         <v>428</v>
       </c>
@@ -35055,7 +35066,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="426" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A426" s="1">
         <v>429</v>
       </c>
@@ -35134,7 +35145,7 @@
       <c r="Z426" s="3"/>
       <c r="AA426" s="3"/>
     </row>
-    <row r="427" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A427">
         <v>429</v>
       </c>
@@ -35217,7 +35228,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="428" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A428">
         <v>429</v>
       </c>
@@ -35300,7 +35311,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="429" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A429">
         <v>429</v>
       </c>
@@ -35383,7 +35394,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="430" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A430">
         <v>429</v>
       </c>
@@ -35466,7 +35477,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="431" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A431">
         <v>429</v>
       </c>
@@ -35549,7 +35560,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="432" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A432">
         <v>429</v>
       </c>
@@ -35632,7 +35643,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="433" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A433" s="1">
         <v>430</v>
       </c>
@@ -35711,7 +35722,7 @@
       <c r="Z433" s="3"/>
       <c r="AA433" s="3"/>
     </row>
-    <row r="434" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A434">
         <v>430</v>
       </c>
@@ -35794,7 +35805,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="435" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A435">
         <v>430</v>
       </c>
@@ -35877,7 +35888,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="436" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A436">
         <v>430</v>
       </c>
@@ -35960,7 +35971,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="437" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A437">
         <v>430</v>
       </c>
@@ -36122,7 +36133,7 @@
       <c r="Z438" s="3"/>
       <c r="AA438" s="3"/>
     </row>
-    <row r="439" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A439">
         <v>433</v>
       </c>
@@ -36205,7 +36216,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="440" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A440">
         <v>433</v>
       </c>
@@ -36288,7 +36299,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="441" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A441">
         <v>433</v>
       </c>
@@ -36371,7 +36382,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="442" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A442">
         <v>433</v>
       </c>
@@ -36450,7 +36461,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="443" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A443">
         <v>433</v>
       </c>
@@ -36527,7 +36538,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="444" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A444">
         <v>433</v>
       </c>
@@ -36608,7 +36619,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="445" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A445">
         <v>433</v>
       </c>
@@ -36749,7 +36760,7 @@
       <c r="Z446" s="3"/>
       <c r="AA446" s="3"/>
     </row>
-    <row r="447" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A447">
         <v>435</v>
       </c>
@@ -36832,7 +36843,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="448" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A448">
         <v>435</v>
       </c>
@@ -36915,7 +36926,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="449" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A449">
         <v>435</v>
       </c>
@@ -36998,7 +37009,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="450" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A450">
         <v>435</v>
       </c>
@@ -37081,7 +37092,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="451" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A451">
         <v>435</v>
       </c>
@@ -37164,7 +37175,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="452" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A452">
         <v>435</v>
       </c>
@@ -37247,7 +37258,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="453" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A453" s="1">
         <v>439</v>
       </c>
@@ -37330,7 +37341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="454" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A454">
         <v>439</v>
       </c>
@@ -37413,7 +37424,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="455" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A455">
         <v>439</v>
       </c>
@@ -37496,7 +37507,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="456" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A456" s="1">
         <v>440</v>
       </c>
@@ -37575,7 +37586,7 @@
       <c r="Z456" s="3"/>
       <c r="AA456" s="3"/>
     </row>
-    <row r="457" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A457">
         <v>440</v>
       </c>
@@ -37658,7 +37669,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="458" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A458">
         <v>440</v>
       </c>
@@ -37741,7 +37752,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="459" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A459" s="1">
         <v>444</v>
       </c>
@@ -37802,7 +37813,7 @@
       <c r="Z459" s="3"/>
       <c r="AA459" s="3"/>
     </row>
-    <row r="460" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A460" s="1">
         <v>445</v>
       </c>
@@ -37865,7 +37876,7 @@
       <c r="Z460" s="3"/>
       <c r="AA460" s="3"/>
     </row>
-    <row r="461" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A461" s="1">
         <v>447</v>
       </c>
@@ -37928,7 +37939,7 @@
       <c r="Z461" s="3"/>
       <c r="AA461" s="3"/>
     </row>
-    <row r="462" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A462" s="1">
         <v>448</v>
       </c>
@@ -37991,7 +38002,7 @@
       <c r="Z462" s="3"/>
       <c r="AA462" s="3"/>
     </row>
-    <row r="463" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A463" s="1">
         <v>451</v>
       </c>
@@ -38054,7 +38065,7 @@
       <c r="Z463" s="3"/>
       <c r="AA463" s="3"/>
     </row>
-    <row r="464" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A464" s="1">
         <v>452</v>
       </c>
@@ -38117,7 +38128,7 @@
       <c r="Z464" s="3"/>
       <c r="AA464" s="3"/>
     </row>
-    <row r="465" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A465" s="1">
         <v>466</v>
       </c>
@@ -38180,7 +38191,7 @@
       <c r="Z465" s="3"/>
       <c r="AA465" s="3"/>
     </row>
-    <row r="466" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A466" s="1">
         <v>467</v>
       </c>
@@ -38243,7 +38254,7 @@
       <c r="Z466" s="3"/>
       <c r="AA466" s="3"/>
     </row>
-    <row r="467" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A467" s="1">
         <v>468</v>
       </c>
@@ -38306,7 +38317,7 @@
       <c r="Z467" s="3"/>
       <c r="AA467" s="3"/>
     </row>
-    <row r="468" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A468" s="1">
         <v>473</v>
       </c>
@@ -38385,7 +38396,7 @@
       <c r="Z468" s="3"/>
       <c r="AA468" s="3"/>
     </row>
-    <row r="469" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A469">
         <v>473</v>
       </c>
@@ -38468,7 +38479,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="470" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A470">
         <v>473</v>
       </c>
@@ -38551,7 +38562,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="471" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A471">
         <v>473</v>
       </c>
@@ -38634,7 +38645,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="472" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A472" s="1">
         <v>474</v>
       </c>
@@ -38709,7 +38720,7 @@
       <c r="Z472" s="3"/>
       <c r="AA472" s="3"/>
     </row>
-    <row r="473" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A473">
         <v>474</v>
       </c>
@@ -38789,7 +38800,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="474" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A474">
         <v>474</v>
       </c>
@@ -38869,7 +38880,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="475" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A475">
         <v>474</v>
       </c>
@@ -38949,7 +38960,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="476" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A476">
         <v>474</v>
       </c>
@@ -39029,7 +39040,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="477" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A477">
         <v>474</v>
       </c>
@@ -39109,7 +39120,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="478" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A478">
         <v>474</v>
       </c>
@@ -39189,7 +39200,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="479" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A479">
         <v>474</v>
       </c>
@@ -39269,7 +39280,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="480" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A480">
         <v>474</v>
       </c>
@@ -39349,7 +39360,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="481" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A481">
         <v>474</v>
       </c>
@@ -39429,7 +39440,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="482" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A482">
         <v>474</v>
       </c>
@@ -39509,7 +39520,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="483" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A483">
         <v>474</v>
       </c>
@@ -39589,7 +39600,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="484" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A484">
         <v>474</v>
       </c>
@@ -39669,7 +39680,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="485" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A485" s="1">
         <v>475</v>
       </c>
@@ -39732,7 +39743,7 @@
       <c r="Z485" s="3"/>
       <c r="AA485" s="3"/>
     </row>
-    <row r="486" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A486" s="1">
         <v>476</v>
       </c>
@@ -39815,7 +39826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="487" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A487">
         <v>476</v>
       </c>
@@ -39898,7 +39909,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="488" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A488">
         <v>476</v>
       </c>
@@ -39981,7 +39992,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="489" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A489">
         <v>476</v>
       </c>
@@ -40064,7 +40075,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="490" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A490" s="1">
         <v>477</v>
       </c>
@@ -40137,7 +40148,7 @@
       <c r="Z490" s="3"/>
       <c r="AA490" s="3"/>
     </row>
-    <row r="491" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A491">
         <v>477</v>
       </c>
@@ -40217,7 +40228,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="492" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A492">
         <v>477</v>
       </c>
@@ -40297,7 +40308,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="493" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A493">
         <v>477</v>
       </c>
@@ -40377,7 +40388,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="494" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A494">
         <v>477</v>
       </c>
@@ -40457,7 +40468,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="495" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A495">
         <v>477</v>
       </c>
@@ -40537,7 +40548,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="496" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A496">
         <v>477</v>
       </c>
@@ -40617,7 +40628,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="497" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A497">
         <v>477</v>
       </c>
@@ -40697,7 +40708,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="498" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A498">
         <v>477</v>
       </c>
@@ -40777,7 +40788,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="499" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A499">
         <v>477</v>
       </c>
@@ -40857,7 +40868,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="500" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A500">
         <v>477</v>
       </c>
@@ -40937,7 +40948,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="501" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A501">
         <v>477</v>
       </c>
@@ -41017,7 +41028,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="502" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A502">
         <v>477</v>
       </c>
@@ -41097,7 +41108,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="503" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A503" s="1">
         <v>478</v>
       </c>
@@ -41176,7 +41187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="504" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A504">
         <v>478</v>
       </c>
@@ -41256,7 +41267,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="505" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A505">
         <v>478</v>
       </c>
@@ -41336,7 +41347,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="506" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A506">
         <v>478</v>
       </c>
@@ -41416,7 +41427,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="507" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A507">
         <v>478</v>
       </c>
@@ -41496,7 +41507,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="508" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A508">
         <v>478</v>
       </c>
@@ -41576,7 +41587,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="509" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A509">
         <v>478</v>
       </c>
@@ -41656,7 +41667,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="510" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A510">
         <v>478</v>
       </c>
@@ -41736,7 +41747,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="511" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A511">
         <v>478</v>
       </c>
@@ -41816,7 +41827,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="512" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A512">
         <v>478</v>
       </c>
@@ -41896,7 +41907,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="513" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A513">
         <v>478</v>
       </c>
@@ -41976,7 +41987,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="514" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A514">
         <v>478</v>
       </c>
@@ -42056,7 +42067,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="515" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A515">
         <v>478</v>
       </c>
@@ -42136,7 +42147,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="516" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A516" s="1">
         <v>479</v>
       </c>
@@ -42215,7 +42226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="517" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A517">
         <v>479</v>
       </c>
@@ -42298,7 +42309,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="518" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A518">
         <v>479</v>
       </c>
@@ -42381,7 +42392,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="519" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A519">
         <v>479</v>
       </c>
@@ -42464,7 +42475,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="520" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A520">
         <v>479</v>
       </c>
@@ -42547,7 +42558,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="521" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A521">
         <v>479</v>
       </c>
@@ -42630,7 +42641,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="522" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A522">
         <v>479</v>
       </c>
@@ -42713,7 +42724,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="523" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A523">
         <v>479</v>
       </c>
@@ -42796,7 +42807,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="524" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A524">
         <v>479</v>
       </c>
@@ -42879,7 +42890,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="525" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A525">
         <v>479</v>
       </c>
@@ -42962,7 +42973,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="526" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A526">
         <v>479</v>
       </c>
@@ -43045,7 +43056,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="527" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A527">
         <v>479</v>
       </c>
@@ -43128,7 +43139,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="528" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A528">
         <v>479</v>
       </c>
@@ -43211,7 +43222,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="529" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A529" s="1">
         <v>480</v>
       </c>
@@ -43286,7 +43297,7 @@
       <c r="Z529" s="3"/>
       <c r="AA529" s="3"/>
     </row>
-    <row r="530" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A530">
         <v>480</v>
       </c>
@@ -43369,7 +43380,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="531" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A531">
         <v>480</v>
       </c>
@@ -43452,7 +43463,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="532" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A532">
         <v>480</v>
       </c>
@@ -43535,7 +43546,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="533" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A533">
         <v>480</v>
       </c>
@@ -43618,7 +43629,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="534" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A534">
         <v>480</v>
       </c>
@@ -43701,7 +43712,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="535" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A535">
         <v>480</v>
       </c>
@@ -43784,7 +43795,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="536" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A536">
         <v>480</v>
       </c>
@@ -43867,7 +43878,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="537" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A537">
         <v>480</v>
       </c>
@@ -43950,7 +43961,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="538" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A538">
         <v>480</v>
       </c>
@@ -44033,7 +44044,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="539" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A539">
         <v>480</v>
       </c>
@@ -44116,7 +44127,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="540" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A540">
         <v>480</v>
       </c>
@@ -44199,7 +44210,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="541" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A541">
         <v>480</v>
       </c>
@@ -44282,7 +44293,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="542" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A542" s="1">
         <v>481</v>
       </c>
@@ -44345,7 +44356,7 @@
       <c r="Z542" s="3"/>
       <c r="AA542" s="3"/>
     </row>
-    <row r="543" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A543">
         <v>481</v>
       </c>
@@ -44421,7 +44432,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="544" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A544" s="1">
         <v>486</v>
       </c>
@@ -44484,7 +44495,7 @@
       <c r="Z544" s="3"/>
       <c r="AA544" s="3"/>
     </row>
-    <row r="545" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A545" s="1">
         <v>506</v>
       </c>
@@ -44545,7 +44556,7 @@
       <c r="Z545" s="3"/>
       <c r="AA545" s="3"/>
     </row>
-    <row r="546" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A546" s="1">
         <v>507</v>
       </c>
@@ -44665,7 +44676,7 @@
       <c r="Z547" s="3"/>
       <c r="AA547" s="3"/>
     </row>
-    <row r="548" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A548" s="1">
         <v>515</v>
       </c>
@@ -44722,7 +44733,7 @@
       <c r="Z548" s="3"/>
       <c r="AA548" s="3"/>
     </row>
-    <row r="549" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A549" s="1">
         <v>516</v>
       </c>
@@ -44779,7 +44790,7 @@
       <c r="Z549" s="3"/>
       <c r="AA549" s="3"/>
     </row>
-    <row r="550" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A550" s="1">
         <v>519</v>
       </c>
@@ -44858,7 +44869,7 @@
       <c r="Z550" s="3"/>
       <c r="AA550" s="3"/>
     </row>
-    <row r="551" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A551">
         <v>519</v>
       </c>
@@ -44941,7 +44952,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="552" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A552">
         <v>519</v>
       </c>
@@ -45024,7 +45035,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="553" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A553" s="1">
         <v>523</v>
       </c>
@@ -45103,7 +45114,7 @@
       <c r="Z553" s="3"/>
       <c r="AA553" s="3"/>
     </row>
-    <row r="554" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A554">
         <v>523</v>
       </c>
@@ -45186,7 +45197,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="555" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A555">
         <v>523</v>
       </c>
@@ -45269,7 +45280,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="556" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A556">
         <v>523</v>
       </c>
@@ -45352,7 +45363,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="557" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A557" s="1">
         <v>524</v>
       </c>
@@ -45431,7 +45442,7 @@
       <c r="Z557" s="3"/>
       <c r="AA557" s="3"/>
     </row>
-    <row r="558" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A558">
         <v>524</v>
       </c>
@@ -45514,7 +45525,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="559" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A559">
         <v>524</v>
       </c>
@@ -45597,7 +45608,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="560" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A560">
         <v>524</v>
       </c>
@@ -45680,7 +45691,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="561" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A561">
         <v>524</v>
       </c>
@@ -45763,7 +45774,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="562" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A562">
         <v>524</v>
       </c>
@@ -45846,7 +45857,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="563" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A563">
         <v>524</v>
       </c>
@@ -45929,7 +45940,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="564" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A564" s="1">
         <v>530</v>
       </c>
@@ -45986,7 +45997,7 @@
       <c r="Z564" s="3"/>
       <c r="AA564" s="3"/>
     </row>
-    <row r="565" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A565" s="1">
         <v>531</v>
       </c>
@@ -46043,7 +46054,7 @@
       <c r="Z565" s="3"/>
       <c r="AA565" s="3"/>
     </row>
-    <row r="566" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A566" s="1">
         <v>532</v>
       </c>
@@ -46114,7 +46125,7 @@
       <c r="Z566" s="3"/>
       <c r="AA566" s="3"/>
     </row>
-    <row r="567" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A567">
         <v>532</v>
       </c>
@@ -46197,7 +46208,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="568" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A568">
         <v>532</v>
       </c>
@@ -46280,7 +46291,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="569" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A569">
         <v>532</v>
       </c>
@@ -46363,7 +46374,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="570" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A570">
         <v>532</v>
       </c>
@@ -46446,7 +46457,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="571" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A571" s="1">
         <v>533</v>
       </c>
@@ -46525,7 +46536,7 @@
       <c r="Z571" s="3"/>
       <c r="AA571" s="3"/>
     </row>
-    <row r="572" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A572">
         <v>533</v>
       </c>
@@ -46608,7 +46619,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="573" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A573">
         <v>533</v>
       </c>
@@ -46691,7 +46702,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="574" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A574" s="1">
         <v>534</v>
       </c>
@@ -46770,7 +46781,7 @@
       <c r="Z574" s="3"/>
       <c r="AA574" s="3"/>
     </row>
-    <row r="575" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A575">
         <v>534</v>
       </c>
@@ -46853,7 +46864,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="576" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A576">
         <v>534</v>
       </c>
@@ -46936,7 +46947,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="577" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A577" s="1">
         <v>535</v>
       </c>
@@ -47015,7 +47026,7 @@
       <c r="Z577" s="3"/>
       <c r="AA577" s="3"/>
     </row>
-    <row r="578" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A578">
         <v>535</v>
       </c>
@@ -47098,7 +47109,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="579" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A579">
         <v>535</v>
       </c>
@@ -47181,7 +47192,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="580" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A580" s="1">
         <v>536</v>
       </c>
@@ -47260,7 +47271,7 @@
       <c r="Z580" s="3"/>
       <c r="AA580" s="3"/>
     </row>
-    <row r="581" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A581">
         <v>536</v>
       </c>
@@ -47343,7 +47354,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="582" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A582">
         <v>536</v>
       </c>
@@ -47426,7 +47437,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="583" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A583" s="1">
         <v>537</v>
       </c>
@@ -47485,7 +47496,7 @@
       <c r="Z583" s="3"/>
       <c r="AA583" s="3"/>
     </row>
-    <row r="584" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A584" s="1">
         <v>538</v>
       </c>
@@ -47542,7 +47553,7 @@
       <c r="Z584" s="3"/>
       <c r="AA584" s="3"/>
     </row>
-    <row r="585" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A585" s="1">
         <v>539</v>
       </c>
@@ -47599,7 +47610,7 @@
       <c r="Z585" s="3"/>
       <c r="AA585" s="3"/>
     </row>
-    <row r="586" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A586" s="1">
         <v>540</v>
       </c>
@@ -47658,7 +47669,7 @@
       <c r="Z586" s="3"/>
       <c r="AA586" s="3"/>
     </row>
-    <row r="587" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A587" s="1">
         <v>543</v>
       </c>
@@ -47735,7 +47746,7 @@
       <c r="Z587" s="3"/>
       <c r="AA587" s="3"/>
     </row>
-    <row r="588" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A588">
         <v>543</v>
       </c>
@@ -47818,7 +47829,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="589" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A589">
         <v>543</v>
       </c>
@@ -47901,7 +47912,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="590" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A590" s="1">
         <v>544</v>
       </c>
@@ -47980,7 +47991,7 @@
       <c r="Z590" s="3"/>
       <c r="AA590" s="3"/>
     </row>
-    <row r="591" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A591">
         <v>544</v>
       </c>
@@ -48063,7 +48074,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="592" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A592">
         <v>544</v>
       </c>
@@ -48146,7 +48157,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="593" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A593">
         <v>544</v>
       </c>
@@ -48229,7 +48240,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="594" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A594">
         <v>544</v>
       </c>
@@ -48312,7 +48323,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="595" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A595" s="1">
         <v>550</v>
       </c>
@@ -48371,7 +48382,7 @@
       <c r="Z595" s="3"/>
       <c r="AA595" s="3"/>
     </row>
-    <row r="596" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A596" s="1">
         <v>551</v>
       </c>
@@ -48430,7 +48441,7 @@
       <c r="Z596" s="3"/>
       <c r="AA596" s="3"/>
     </row>
-    <row r="597" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A597" s="1">
         <v>554</v>
       </c>
@@ -48487,7 +48498,7 @@
       <c r="Z597" s="3"/>
       <c r="AA597" s="3"/>
     </row>
-    <row r="598" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A598" s="1">
         <v>555</v>
       </c>
@@ -48544,7 +48555,7 @@
       <c r="Z598" s="3"/>
       <c r="AA598" s="3"/>
     </row>
-    <row r="599" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A599" s="1">
         <v>69</v>
       </c>
@@ -48627,7 +48638,7 @@
         <v>85.129118432769005</v>
       </c>
     </row>
-    <row r="600" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A600" s="1">
         <v>111</v>
       </c>
@@ -48708,7 +48719,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="601" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A601" s="1">
         <v>197</v>
       </c>
@@ -48791,7 +48802,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="602" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A602" s="1">
         <v>213</v>
       </c>
@@ -48874,7 +48885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="603" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A603">
         <v>213</v>
       </c>
@@ -48957,7 +48968,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="604" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A604">
         <v>213</v>
       </c>
@@ -49040,7 +49051,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="605" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A605">
         <v>213</v>
       </c>
@@ -49123,7 +49134,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="606" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A606">
         <v>213</v>
       </c>
@@ -49206,7 +49217,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="607" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A607">
         <v>213</v>
       </c>
@@ -49289,7 +49300,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="608" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A608">
         <v>213</v>
       </c>
@@ -49372,7 +49383,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="609" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A609">
         <v>213</v>
       </c>
@@ -49455,7 +49466,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="610" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A610">
         <v>213</v>
       </c>
@@ -49538,7 +49549,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="611" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="611" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A611" s="1">
         <v>233</v>
       </c>
@@ -49617,7 +49628,7 @@
       <c r="Z611" s="3"/>
       <c r="AA611" s="3"/>
     </row>
-    <row r="612" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A612" s="1">
         <v>234</v>
       </c>
@@ -49779,7 +49790,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="614" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A614">
         <v>238</v>
       </c>
@@ -49862,7 +49873,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="615" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A615">
         <v>238</v>
       </c>
@@ -49945,7 +49956,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="616" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A616">
         <v>238</v>
       </c>
@@ -50028,7 +50039,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="617" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="617" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A617">
         <v>238</v>
       </c>
@@ -50111,7 +50122,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="618" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="618" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A618">
         <v>238</v>
       </c>
@@ -50194,7 +50205,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="619" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="619" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A619">
         <v>238</v>
       </c>
@@ -50277,7 +50288,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="620" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="620" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A620">
         <v>238</v>
       </c>
@@ -50360,7 +50371,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="621" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="621" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A621">
         <v>238</v>
       </c>
@@ -50443,7 +50454,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="622" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="622" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A622" s="1">
         <v>240</v>
       </c>
@@ -50522,7 +50533,7 @@
       <c r="Z622" s="3"/>
       <c r="AA622" s="3"/>
     </row>
-    <row r="623" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="623" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A623" s="1">
         <v>251</v>
       </c>
@@ -50599,7 +50610,7 @@
       <c r="Z623" s="3"/>
       <c r="AA623" s="3"/>
     </row>
-    <row r="624" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="624" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A624" s="1">
         <v>254</v>
       </c>
@@ -50655,7 +50666,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="625" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="625" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A625" s="1">
         <v>263</v>
       </c>
@@ -50734,7 +50745,7 @@
       <c r="Z625" s="3"/>
       <c r="AA625" s="3"/>
     </row>
-    <row r="626" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="626" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A626" s="1">
         <v>265</v>
       </c>
@@ -50892,7 +50903,7 @@
       <c r="Z627" s="3"/>
       <c r="AA627" s="3"/>
     </row>
-    <row r="628" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="628" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A628" s="1">
         <v>300</v>
       </c>
@@ -50971,7 +50982,7 @@
       <c r="Z628" s="3"/>
       <c r="AA628" s="3"/>
     </row>
-    <row r="629" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="629" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A629" s="1">
         <v>301</v>
       </c>
@@ -51050,7 +51061,7 @@
       <c r="Z629" s="3"/>
       <c r="AA629" s="3"/>
     </row>
-    <row r="630" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A630" s="1">
         <v>306</v>
       </c>
@@ -51133,7 +51144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="631" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="631" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A631">
         <v>306</v>
       </c>
@@ -51216,7 +51227,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="632" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="632" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A632">
         <v>306</v>
       </c>
@@ -51299,7 +51310,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="633" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="633" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A633">
         <v>306</v>
       </c>
@@ -51382,7 +51393,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="634" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="634" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A634">
         <v>306</v>
       </c>
@@ -51465,7 +51476,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="635" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="635" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A635">
         <v>306</v>
       </c>
@@ -51548,7 +51559,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="636" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="636" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A636">
         <v>306</v>
       </c>
@@ -51631,7 +51642,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="637" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="637" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A637" s="1">
         <v>347</v>
       </c>
@@ -51710,7 +51721,7 @@
       <c r="Z637" s="3"/>
       <c r="AA637" s="3"/>
     </row>
-    <row r="638" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="638" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A638" s="1">
         <v>348</v>
       </c>
@@ -51789,7 +51800,7 @@
       <c r="Z638" s="3"/>
       <c r="AA638" s="3"/>
     </row>
-    <row r="639" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="639" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A639" s="1">
         <v>351</v>
       </c>
@@ -51866,7 +51877,7 @@
       <c r="Z639" s="3"/>
       <c r="AA639" s="3"/>
     </row>
-    <row r="640" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="640" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A640" s="1">
         <v>352</v>
       </c>
@@ -51943,7 +51954,7 @@
       <c r="Z640" s="3"/>
       <c r="AA640" s="3"/>
     </row>
-    <row r="641" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="641" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A641" s="1">
         <v>368</v>
       </c>
@@ -52018,7 +52029,7 @@
       <c r="Z641" s="3"/>
       <c r="AA641" s="3"/>
     </row>
-    <row r="642" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="642" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A642" s="1">
         <v>372</v>
       </c>
@@ -52093,7 +52104,7 @@
       <c r="Z642" s="3"/>
       <c r="AA642" s="3"/>
     </row>
-    <row r="643" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="643" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A643" s="1">
         <v>373</v>
       </c>
@@ -52176,7 +52187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="644" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="644" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A644">
         <v>373</v>
       </c>
@@ -52259,7 +52270,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="645" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="645" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A645">
         <v>373</v>
       </c>
@@ -52342,7 +52353,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="646" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="646" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A646">
         <v>373</v>
       </c>
@@ -52425,7 +52436,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="647" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="647" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A647">
         <v>373</v>
       </c>
@@ -52508,7 +52519,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="648" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="648" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A648">
         <v>373</v>
       </c>
@@ -52591,7 +52602,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="649" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="649" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A649">
         <v>373</v>
       </c>
@@ -52674,7 +52685,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="650" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="650" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A650" s="1">
         <v>390</v>
       </c>
@@ -52757,7 +52768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="651" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="651" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A651">
         <v>390</v>
       </c>
@@ -52840,7 +52851,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="652" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="652" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A652">
         <v>390</v>
       </c>
@@ -52923,7 +52934,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="653" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="653" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A653">
         <v>390</v>
       </c>
@@ -53006,7 +53017,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="654" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="654" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A654">
         <v>390</v>
       </c>
@@ -53089,7 +53100,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="655" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="655" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A655">
         <v>390</v>
       </c>
@@ -53172,7 +53183,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="656" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="656" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A656">
         <v>390</v>
       </c>
@@ -53255,7 +53266,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="657" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="657" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A657">
         <v>390</v>
       </c>
@@ -53338,7 +53349,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="658" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="658" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A658">
         <v>390</v>
       </c>
@@ -53421,7 +53432,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="659" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="659" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A659">
         <v>390</v>
       </c>
@@ -53504,7 +53515,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="660" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="660" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A660">
         <v>390</v>
       </c>
@@ -53587,7 +53598,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="661" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="661" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A661">
         <v>390</v>
       </c>
@@ -53670,7 +53681,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="662" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="662" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A662">
         <v>390</v>
       </c>
@@ -53753,7 +53764,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="663" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="663" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A663" s="1">
         <v>394</v>
       </c>
@@ -53832,7 +53843,7 @@
       <c r="Z663" s="3"/>
       <c r="AA663" s="3"/>
     </row>
-    <row r="664" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="664" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A664" s="1">
         <v>395</v>
       </c>
@@ -53909,7 +53920,7 @@
       <c r="Z664" s="3"/>
       <c r="AA664" s="3"/>
     </row>
-    <row r="665" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="665" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A665" s="1">
         <v>409</v>
       </c>
@@ -53986,7 +53997,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="666" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="666" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A666">
         <v>409</v>
       </c>
@@ -54069,7 +54080,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="667" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="667" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A667">
         <v>409</v>
       </c>
@@ -54152,7 +54163,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="668" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="668" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A668" s="1">
         <v>414</v>
       </c>
@@ -54235,7 +54246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="669" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="669" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A669">
         <v>414</v>
       </c>
@@ -54318,7 +54329,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="670" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="670" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A670">
         <v>414</v>
       </c>
@@ -54401,7 +54412,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="671" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="671" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A671">
         <v>414</v>
       </c>
@@ -54484,7 +54495,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="672" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="672" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A672">
         <v>414</v>
       </c>
@@ -54567,7 +54578,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="673" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="673" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A673">
         <v>414</v>
       </c>
@@ -54650,7 +54661,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="674" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="674" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A674">
         <v>414</v>
       </c>
@@ -54733,7 +54744,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="675" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="675" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A675">
         <v>414</v>
       </c>
@@ -54816,7 +54827,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="676" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="676" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A676">
         <v>414</v>
       </c>
@@ -54899,7 +54910,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="677" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="677" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A677">
         <v>414</v>
       </c>
@@ -54982,7 +54993,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="678" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="678" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A678" s="1">
         <v>415</v>
       </c>
@@ -55065,7 +55076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="679" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="679" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A679">
         <v>415</v>
       </c>
@@ -55148,7 +55159,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="680" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="680" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A680">
         <v>415</v>
       </c>
@@ -55231,7 +55242,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="681" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="681" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A681">
         <v>415</v>
       </c>
@@ -55314,7 +55325,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="682" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="682" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A682">
         <v>415</v>
       </c>
@@ -55397,7 +55408,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="683" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="683" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A683">
         <v>415</v>
       </c>
@@ -55480,7 +55491,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="684" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="684" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A684">
         <v>415</v>
       </c>
@@ -55563,7 +55574,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="685" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="685" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A685">
         <v>415</v>
       </c>
@@ -55646,7 +55657,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="686" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="686" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A686">
         <v>415</v>
       </c>
@@ -55729,7 +55740,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="687" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="687" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A687">
         <v>415</v>
       </c>
@@ -55812,7 +55823,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="688" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="688" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A688">
         <v>415</v>
       </c>
@@ -55895,7 +55906,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="689" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="689" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A689">
         <v>415</v>
       </c>
@@ -55978,7 +55989,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="690" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="690" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A690">
         <v>415</v>
       </c>
@@ -56061,7 +56072,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="691" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="691" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A691">
         <v>415</v>
       </c>
@@ -56144,7 +56155,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="692" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="692" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A692">
         <v>415</v>
       </c>
@@ -56227,7 +56238,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="693" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="693" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A693" s="1">
         <v>416</v>
       </c>
@@ -56310,7 +56321,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="694" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="694" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A694">
         <v>416</v>
       </c>
@@ -56393,7 +56404,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="695" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="695" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A695">
         <v>416</v>
       </c>
@@ -56476,7 +56487,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="696" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="696" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A696">
         <v>416</v>
       </c>
@@ -56559,7 +56570,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="697" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="697" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A697">
         <v>416</v>
       </c>
@@ -56642,7 +56653,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="698" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="698" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A698">
         <v>416</v>
       </c>
@@ -56725,7 +56736,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="699" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="699" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A699">
         <v>416</v>
       </c>
@@ -56808,7 +56819,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="700" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="700" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A700" s="1">
         <v>417</v>
       </c>
@@ -56891,7 +56902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="701" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="701" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A701">
         <v>417</v>
       </c>
@@ -56974,7 +56985,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="702" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="702" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A702">
         <v>417</v>
       </c>
@@ -57057,7 +57068,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="703" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="703" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A703">
         <v>417</v>
       </c>
@@ -57140,7 +57151,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="704" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="704" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A704">
         <v>417</v>
       </c>
@@ -57223,7 +57234,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="705" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="705" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A705">
         <v>417</v>
       </c>
@@ -57306,7 +57317,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="706" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="706" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A706">
         <v>417</v>
       </c>
@@ -57389,7 +57400,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="707" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="707" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A707" s="1">
         <v>418</v>
       </c>
@@ -57472,7 +57483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="708" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="708" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A708">
         <v>418</v>
       </c>
@@ -57555,7 +57566,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="709" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="709" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A709">
         <v>418</v>
       </c>
@@ -57638,7 +57649,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="710" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="710" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A710">
         <v>418</v>
       </c>
@@ -57721,7 +57732,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="711" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="711" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A711">
         <v>418</v>
       </c>
@@ -57802,7 +57813,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="712" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="712" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A712">
         <v>418</v>
       </c>
@@ -57885,7 +57896,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="713" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="713" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A713">
         <v>418</v>
       </c>
@@ -57968,7 +57979,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="714" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="714" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A714">
         <v>418</v>
       </c>
@@ -58051,7 +58062,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="715" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="715" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A715">
         <v>418</v>
       </c>
@@ -58134,7 +58145,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="716" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="716" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A716">
         <v>418</v>
       </c>
@@ -58217,7 +58228,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="717" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="717" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A717" s="1">
         <v>420</v>
       </c>
@@ -58300,7 +58311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="718" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="718" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A718">
         <v>420</v>
       </c>
@@ -58383,7 +58394,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="719" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="719" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A719">
         <v>420</v>
       </c>
@@ -58466,7 +58477,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="720" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="720" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A720">
         <v>420</v>
       </c>
@@ -58549,7 +58560,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="721" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="721" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A721">
         <v>420</v>
       </c>
@@ -58632,7 +58643,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="722" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="722" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A722">
         <v>420</v>
       </c>
@@ -58715,7 +58726,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="723" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="723" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A723">
         <v>420</v>
       </c>
@@ -58798,7 +58809,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="724" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="724" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A724" s="1">
         <v>431</v>
       </c>
@@ -58873,7 +58884,7 @@
       <c r="Z724" s="3"/>
       <c r="AA724" s="3"/>
     </row>
-    <row r="725" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="725" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A725" s="1">
         <v>432</v>
       </c>
@@ -58956,7 +58967,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="726" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="726" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A726">
         <v>432</v>
       </c>
@@ -59039,7 +59050,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="727" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="727" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A727">
         <v>432</v>
       </c>
@@ -59122,7 +59133,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="728" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="728" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A728">
         <v>432</v>
       </c>
@@ -59205,7 +59216,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="729" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="729" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A729">
         <v>432</v>
       </c>
@@ -59288,7 +59299,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="730" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="730" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A730">
         <v>432</v>
       </c>
@@ -59371,7 +59382,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="731" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="731" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A731">
         <v>432</v>
       </c>
@@ -59454,7 +59465,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="732" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="732" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A732">
         <v>432</v>
       </c>
@@ -59537,7 +59548,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="733" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="733" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A733">
         <v>432</v>
       </c>
@@ -59620,7 +59631,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="734" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="734" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A734">
         <v>432</v>
       </c>
@@ -59703,7 +59714,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="735" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="735" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A735" s="1">
         <v>453</v>
       </c>
@@ -59774,7 +59785,7 @@
       <c r="Z735" s="3"/>
       <c r="AA735" s="3"/>
     </row>
-    <row r="736" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="736" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A736" s="1">
         <v>455</v>
       </c>
@@ -59841,7 +59852,7 @@
       <c r="Z736" s="3"/>
       <c r="AA736" s="3"/>
     </row>
-    <row r="737" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="737" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A737" s="1">
         <v>456</v>
       </c>
@@ -59922,7 +59933,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="738" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="738" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A738">
         <v>456</v>
       </c>
@@ -60005,7 +60016,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="739" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="739" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A739">
         <v>456</v>
       </c>
@@ -60088,7 +60099,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="740" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="740" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A740">
         <v>456</v>
       </c>
@@ -60171,7 +60182,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="741" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="741" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A741" s="1">
         <v>457</v>
       </c>
@@ -60252,7 +60263,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="742" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="742" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A742">
         <v>457</v>
       </c>
@@ -60335,7 +60346,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="743" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="743" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A743">
         <v>457</v>
       </c>
@@ -60418,7 +60429,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="744" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="744" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A744">
         <v>457</v>
       </c>
@@ -60501,7 +60512,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="745" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="745" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A745" s="1">
         <v>469</v>
       </c>
@@ -60584,7 +60595,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="746" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="746" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A746">
         <v>469</v>
       </c>
@@ -60667,7 +60678,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="747" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="747" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A747">
         <v>469</v>
       </c>
@@ -60750,7 +60761,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="748" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="748" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A748">
         <v>469</v>
       </c>
@@ -60833,7 +60844,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="749" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="749" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A749">
         <v>469</v>
       </c>
@@ -60916,7 +60927,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="750" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="750" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A750">
         <v>469</v>
       </c>
@@ -60999,7 +61010,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="751" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="751" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A751">
         <v>469</v>
       </c>
@@ -61082,7 +61093,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="752" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="752" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A752">
         <v>469</v>
       </c>
@@ -61165,7 +61176,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="753" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="753" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A753">
         <v>469</v>
       </c>
@@ -61248,7 +61259,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="754" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="754" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A754">
         <v>469</v>
       </c>
@@ -61331,7 +61342,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="755" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="755" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A755">
         <v>469</v>
       </c>
@@ -61414,7 +61425,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="756" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="756" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A756" s="1">
         <v>470</v>
       </c>
@@ -61497,7 +61508,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="757" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="757" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A757">
         <v>470</v>
       </c>
@@ -61578,7 +61589,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="758" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="758" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A758">
         <v>470</v>
       </c>
@@ -61661,7 +61672,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="759" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="759" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A759">
         <v>470</v>
       </c>
@@ -61744,7 +61755,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="760" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="760" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A760">
         <v>470</v>
       </c>
@@ -61827,7 +61838,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="761" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="761" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A761">
         <v>470</v>
       </c>
@@ -61910,7 +61921,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="762" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="762" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A762" s="1">
         <v>471</v>
       </c>
@@ -61993,7 +62004,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="763" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="763" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A763">
         <v>471</v>
       </c>
@@ -62076,7 +62087,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="764" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="764" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A764">
         <v>471</v>
       </c>
@@ -62159,7 +62170,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="765" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="765" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A765">
         <v>471</v>
       </c>
@@ -62242,7 +62253,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="766" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="766" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A766">
         <v>471</v>
       </c>
@@ -62325,7 +62336,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="767" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="767" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A767">
         <v>471</v>
       </c>
@@ -62408,7 +62419,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="768" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="768" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A768">
         <v>471</v>
       </c>
@@ -62491,7 +62502,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="769" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="769" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A769">
         <v>471</v>
       </c>
@@ -62574,7 +62585,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="770" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="770" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A770" s="1">
         <v>484</v>
       </c>
@@ -62643,7 +62654,7 @@
       <c r="Z770" s="3"/>
       <c r="AA770" s="3"/>
     </row>
-    <row r="771" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="771" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A771" s="1">
         <v>510</v>
       </c>
@@ -62724,7 +62735,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="772" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="772" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A772">
         <v>510</v>
       </c>
@@ -62801,7 +62812,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="773" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="773" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A773" s="1">
         <v>511</v>
       </c>
@@ -62882,7 +62893,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="774" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="774" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A774">
         <v>511</v>
       </c>
@@ -62965,7 +62976,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="775" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="775" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A775">
         <v>511</v>
       </c>
@@ -63048,7 +63059,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="776" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="776" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A776">
         <v>511</v>
       </c>
@@ -63131,7 +63142,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="777" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="777" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A777">
         <v>511</v>
       </c>
@@ -63214,7 +63225,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="778" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="778" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A778">
         <v>511</v>
       </c>
@@ -63297,7 +63308,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="779" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="779" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A779">
         <v>511</v>
       </c>
@@ -63380,7 +63391,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="780" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="780" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A780">
         <v>511</v>
       </c>
@@ -63463,7 +63474,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="781" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="781" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A781" s="1">
         <v>513</v>
       </c>
@@ -63526,7 +63537,7 @@
       <c r="Z781" s="3"/>
       <c r="AA781" s="3"/>
     </row>
-    <row r="782" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="782" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A782" s="1">
         <v>518</v>
       </c>
@@ -63580,7 +63591,7 @@
       </c>
       <c r="R782" s="3"/>
     </row>
-    <row r="783" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="783" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A783" s="1">
         <v>526</v>
       </c>
@@ -63639,7 +63650,7 @@
       <c r="Z783" s="3"/>
       <c r="AA783" s="3"/>
     </row>
-    <row r="784" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="784" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A784" s="1">
         <v>529</v>
       </c>
@@ -63720,7 +63731,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="785" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="785" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A785">
         <v>529</v>
       </c>
@@ -63803,7 +63814,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="786" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="786" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A786">
         <v>529</v>
       </c>
@@ -63888,6 +63899,11 @@
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
+  <autoFilter ref="A1:AA786" xr:uid="{2B479DA7-9079-4551-A26B-76000E86CFA4}">
+    <filterColumn colId="0">
+      <colorFilter dxfId="0"/>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AA786">
     <sortCondition ref="F2:F786"/>
   </sortState>

--- a/data/raw/Kawak/2025.xlsx
+++ b/data/raw/Kawak/2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://poligran-my.sharepoint.com/personal/lxisilva_poligran_edu_co/Documents/Documentos/Proyectos/Sistema_Indicadores_Poli/data/raw/Kawak/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Sistema_Indicadores_Poli/data/raw/Kawak/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B34FD21E-5942-44C7-BEC5-20DF45701E1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{B34FD21E-5942-44C7-BEC5-20DF45701E1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{027D18F3-E653-4E84-8642-7EDAF4789F07}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{CF5C8F99-ADA8-44DF-B65E-B583EA4B64F8}"/>
   </bookViews>
@@ -3671,7 +3671,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -3683,6 +3683,7 @@
       <sz val="11"/>
       <color indexed="8"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="8">
@@ -3759,7 +3760,9 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{4534F693-95A5-4B0C-9740-84EC29E45796}"/>
+  </tableStyles>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>

--- a/data/raw/Kawak/2025.xlsx
+++ b/data/raw/Kawak/2025.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Sistema_Indicadores_Poli/data/raw/Kawak/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{B34FD21E-5942-44C7-BEC5-20DF45701E1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{027D18F3-E653-4E84-8642-7EDAF4789F07}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="8_{B34FD21E-5942-44C7-BEC5-20DF45701E1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{93C878D7-F2B9-43EC-9DCE-E55E00D96B9B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{CF5C8F99-ADA8-44DF-B65E-B583EA4B64F8}"/>
   </bookViews>
   <sheets>
     <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Worksheet!$A$1:$AA$786</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">

--- a/data/raw/Kawak/2025.xlsx
+++ b/data/raw/Kawak/2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Sistema_Indicadores_Poli/data/raw/Kawak/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="8_{B34FD21E-5942-44C7-BEC5-20DF45701E1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{93C878D7-F2B9-43EC-9DCE-E55E00D96B9B}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="8_{B34FD21E-5942-44C7-BEC5-20DF45701E1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{468C7375-D35C-4D38-9BE9-4BA6E01865C8}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{CF5C8F99-ADA8-44DF-B65E-B583EA4B64F8}"/>
   </bookViews>
@@ -4162,14 +4162,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1600AA31-E3D5-4986-B5AC-C7A7BAEED592}">
-  <dimension ref="A1:AA786"/>
+  <dimension ref="A1:AB786"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="27" width="9.109375" customWidth="1"/>
     <col min="28" max="256" width="8.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -4251,8 +4251,9 @@
       <c r="AA1" s="2" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB1" s="2"/>
+    </row>
+    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>68</v>
       </c>
@@ -4300,7 +4301,7 @@
         <v>85.3</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>69</v>
       </c>
@@ -4354,7 +4355,7 @@
         <v>90.75</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>73</v>
       </c>
@@ -4402,7 +4403,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>74</v>
       </c>
@@ -4450,7 +4451,7 @@
         <v>91.49</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>77</v>
       </c>
@@ -4528,7 +4529,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>84</v>
       </c>
@@ -4576,7 +4577,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>85</v>
       </c>
@@ -4624,7 +4625,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>86</v>
       </c>
@@ -4672,7 +4673,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>87</v>
       </c>
@@ -4720,7 +4721,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>88</v>
       </c>
@@ -4768,7 +4769,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>89</v>
       </c>
@@ -4816,7 +4817,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>90</v>
       </c>
@@ -4864,7 +4865,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>91</v>
       </c>
@@ -4912,7 +4913,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>92</v>
       </c>
@@ -4960,7 +4961,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>94</v>
       </c>
